--- a/Source Code/b.10 Dataset C&C UCI ML (Selected) MrMiMaxG-CVM/d. prediction results M4 dataset C&C UCI ML.xlsx
+++ b/Source Code/b.10 Dataset C&C UCI ML (Selected) MrMiMaxG-CVM/d. prediction results M4 dataset C&C UCI ML.xlsx
@@ -455,13 +455,13 @@
         <v>0.22</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1658958542064758</v>
+        <v>0.1696189892815826</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05410414579352421</v>
+        <v>0.05038101071841736</v>
       </c>
       <c r="D2" t="n">
-        <v>24.592793542511</v>
+        <v>22.90045941746244</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>0.04</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05206748858352483</v>
+        <v>0.03813949890025359</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01206748858352483</v>
+        <v>0.001860501099746413</v>
       </c>
       <c r="D3" t="n">
-        <v>30.16872145881209</v>
+        <v>4.651252749366033</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1329677921447827</v>
+        <v>0.1436247967958203</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03296779214478271</v>
+        <v>0.04362479679582029</v>
       </c>
       <c r="D4" t="n">
-        <v>32.96779214478271</v>
+        <v>43.62479679582029</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>0.08</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07760919804189381</v>
+        <v>0.08372947001864639</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00239080195810619</v>
+        <v>0.003729470018646389</v>
       </c>
       <c r="D5" t="n">
-        <v>2.988502447632737</v>
+        <v>4.661837523307986</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>0.04</v>
       </c>
       <c r="B6" t="n">
-        <v>0.05336760238631322</v>
+        <v>0.02992953816727145</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01336760238631322</v>
+        <v>0.01007046183272855</v>
       </c>
       <c r="D6" t="n">
-        <v>33.41900596578304</v>
+        <v>25.17615458182137</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>0.05</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1077507655339287</v>
+        <v>0.1161106431273871</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0577507655339287</v>
+        <v>0.06611064312738706</v>
       </c>
       <c r="D7" t="n">
-        <v>115.5015310678574</v>
+        <v>132.2212862547741</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>0.23</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2691986325574295</v>
+        <v>0.2678662678365168</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03919863255742947</v>
+        <v>0.03786626783651678</v>
       </c>
       <c r="D8" t="n">
-        <v>17.04288372062151</v>
+        <v>16.46359471152903</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>0.48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5164278444298422</v>
+        <v>0.5167439646127638</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03642784442984226</v>
+        <v>0.03674396461276386</v>
       </c>
       <c r="D9" t="n">
-        <v>7.589134256217138</v>
+        <v>7.654992627659138</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>0.04</v>
       </c>
       <c r="B10" t="n">
-        <v>0.05672786845357369</v>
+        <v>0.03948622618726805</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01672786845357369</v>
+        <v>0.0005137738127319533</v>
       </c>
       <c r="D10" t="n">
-        <v>41.81967113393423</v>
+        <v>1.284434531829883</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>0.2</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3476808682190838</v>
+        <v>0.3355800151214758</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1476808682190838</v>
+        <v>0.1355800151214758</v>
       </c>
       <c r="D11" t="n">
-        <v>73.8404341095419</v>
+        <v>67.79000756073791</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>0.63</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5324693603426217</v>
+        <v>0.4932384830503169</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09753063965737829</v>
+        <v>0.1367615169496831</v>
       </c>
       <c r="D12" t="n">
-        <v>15.48105391386957</v>
+        <v>21.70817729360049</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1276018458476877</v>
+        <v>0.1354723802210495</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02760184584768774</v>
+        <v>0.03547238022104945</v>
       </c>
       <c r="D13" t="n">
-        <v>27.60184584768774</v>
+        <v>35.47238022104946</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1481735326334253</v>
+        <v>0.09177878655881666</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07817353263342525</v>
+        <v>0.02177878655881665</v>
       </c>
       <c r="D14" t="n">
-        <v>111.6764751906075</v>
+        <v>31.11255222688093</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>0.11</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1190152811579439</v>
+        <v>0.1369773754751922</v>
       </c>
       <c r="C15" t="n">
-        <v>0.009015281157943908</v>
+        <v>0.02697737547519218</v>
       </c>
       <c r="D15" t="n">
-        <v>8.195710143585371</v>
+        <v>24.52488679562925</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>0.05</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1232157091357381</v>
+        <v>0.1353517680554542</v>
       </c>
       <c r="C16" t="n">
-        <v>0.07321570913573809</v>
+        <v>0.08535176805545418</v>
       </c>
       <c r="D16" t="n">
-        <v>146.4314182714762</v>
+        <v>170.7035361109083</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>0.04</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05844167840544223</v>
+        <v>0.03963774569780831</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01844167840544223</v>
+        <v>0.0003622543021916877</v>
       </c>
       <c r="D17" t="n">
-        <v>46.10419601360557</v>
+        <v>0.9056357554792193</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>0.17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1316998221515726</v>
+        <v>0.1562984254191152</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0383001778484274</v>
+        <v>0.01370157458088481</v>
       </c>
       <c r="D18" t="n">
-        <v>22.52951638142788</v>
+        <v>8.05974975346165</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>0.51</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5182814015272358</v>
+        <v>0.4840549405736774</v>
       </c>
       <c r="C19" t="n">
-        <v>0.008281401527235777</v>
+        <v>0.02594505942632258</v>
       </c>
       <c r="D19" t="n">
-        <v>1.623804221026623</v>
+        <v>5.087266554180898</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>0.52</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4698532077331219</v>
+        <v>0.4680145011583406</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05014679226687813</v>
+        <v>0.05198549884165943</v>
       </c>
       <c r="D20" t="n">
-        <v>9.643613897476563</v>
+        <v>9.997211315703735</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>0.16</v>
       </c>
       <c r="B21" t="n">
-        <v>0.07319715945977368</v>
+        <v>0.0457394174728501</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08680284054022633</v>
+        <v>0.1142605825271499</v>
       </c>
       <c r="D21" t="n">
-        <v>54.25177533764145</v>
+        <v>71.41286407946869</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>0.01</v>
       </c>
       <c r="B22" t="n">
-        <v>0.05614673825272909</v>
+        <v>0.005048416242030396</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04614673825272909</v>
+        <v>0.004951583757969604</v>
       </c>
       <c r="D22" t="n">
-        <v>461.4673825272909</v>
+        <v>49.51583757969604</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>0.47</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2610120764033519</v>
+        <v>0.2580541665294065</v>
       </c>
       <c r="C23" t="n">
-        <v>0.208987923596648</v>
+        <v>0.2119458334705935</v>
       </c>
       <c r="D23" t="n">
-        <v>44.46551565886129</v>
+        <v>45.09485818523265</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>0.21</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1245379432897106</v>
+        <v>0.1515711616167845</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08546205671028942</v>
+        <v>0.05842883838321547</v>
       </c>
       <c r="D24" t="n">
-        <v>40.6962174810902</v>
+        <v>27.82325637295975</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>0.27</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1027272390244851</v>
+        <v>0.1138438122143639</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1672727609755149</v>
+        <v>0.1561561877856361</v>
       </c>
       <c r="D25" t="n">
-        <v>61.95287443537589</v>
+        <v>57.83562510579115</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>0.06</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0605671765709509</v>
+        <v>0.07750562262674798</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0005671765709509002</v>
+        <v>0.01750562262674799</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9452942849181671</v>
+        <v>29.17603771124664</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>0.11</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1309705429009789</v>
+        <v>0.1457751430822233</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02097054290097887</v>
+        <v>0.03577514308222328</v>
       </c>
       <c r="D27" t="n">
-        <v>19.06412990998079</v>
+        <v>32.52285734747571</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>0.45</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2878636881450635</v>
+        <v>0.1949196064843365</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1621363118549365</v>
+        <v>0.2550803935156635</v>
       </c>
       <c r="D28" t="n">
-        <v>36.03029152331923</v>
+        <v>56.68453189236966</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>0.41</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5148046301931852</v>
+        <v>0.5262287011400448</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1048046301931853</v>
+        <v>0.1162287011400449</v>
       </c>
       <c r="D29" t="n">
-        <v>25.56210492516714</v>
+        <v>28.34846369269387</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>0.14</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1979483951226</v>
+        <v>0.196625010356163</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05794839512260003</v>
+        <v>0.05662501035616302</v>
       </c>
       <c r="D30" t="n">
-        <v>41.39171080185716</v>
+        <v>40.44643596868787</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>0.11</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1429235682572731</v>
+        <v>0.1318463162531655</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03292356825727309</v>
+        <v>0.02184631625316551</v>
       </c>
       <c r="D31" t="n">
-        <v>29.930516597521</v>
+        <v>19.86028750287773</v>
       </c>
     </row>
     <row r="32">
@@ -875,13 +875,13 @@
         <v>0.25</v>
       </c>
       <c r="B32" t="n">
-        <v>0.584344709495447</v>
+        <v>0.5878550697814613</v>
       </c>
       <c r="C32" t="n">
-        <v>0.334344709495447</v>
+        <v>0.3378550697814613</v>
       </c>
       <c r="D32" t="n">
-        <v>133.7378837981788</v>
+        <v>135.1420279125845</v>
       </c>
     </row>
     <row r="33">
@@ -889,13 +889,13 @@
         <v>0.06</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0613817177833158</v>
+        <v>0.07049595374435808</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001381717783315806</v>
+        <v>0.01049595374435808</v>
       </c>
       <c r="D33" t="n">
-        <v>2.302862972193009</v>
+        <v>17.4932562405968</v>
       </c>
     </row>
     <row r="34">
@@ -903,13 +903,13 @@
         <v>0.59</v>
       </c>
       <c r="B34" t="n">
-        <v>0.5272107392496104</v>
+        <v>0.6041621259950081</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0627892607503896</v>
+        <v>0.0141621259950081</v>
       </c>
       <c r="D34" t="n">
-        <v>10.6422475848118</v>
+        <v>2.400360338136966</v>
       </c>
     </row>
     <row r="35">
@@ -917,13 +917,13 @@
         <v>0.08</v>
       </c>
       <c r="B35" t="n">
-        <v>0.06402705723288293</v>
+        <v>0.08419248263833357</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01597294276711707</v>
+        <v>0.004192482638333564</v>
       </c>
       <c r="D35" t="n">
-        <v>19.96617845889634</v>
+        <v>5.240603297916955</v>
       </c>
     </row>
     <row r="36">
@@ -931,13 +931,13 @@
         <v>0.19</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2663245325615248</v>
+        <v>0.3211206915138746</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07632453256152477</v>
+        <v>0.1311206915138746</v>
       </c>
       <c r="D36" t="n">
-        <v>40.17080661132882</v>
+        <v>69.01089027046029</v>
       </c>
     </row>
     <row r="37">
@@ -945,13 +945,13 @@
         <v>0.06</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1337738160354509</v>
+        <v>0.1378367336287026</v>
       </c>
       <c r="C37" t="n">
-        <v>0.07377381603545086</v>
+        <v>0.07783673362870258</v>
       </c>
       <c r="D37" t="n">
-        <v>122.9563600590848</v>
+        <v>129.727889381171</v>
       </c>
     </row>
     <row r="38">
@@ -959,13 +959,13 @@
         <v>0.04</v>
       </c>
       <c r="B38" t="n">
-        <v>0.05281497710806937</v>
+        <v>0.007807720005523655</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01281497710806937</v>
+        <v>0.03219227999447635</v>
       </c>
       <c r="D38" t="n">
-        <v>32.03744277017343</v>
+        <v>80.48069998619086</v>
       </c>
     </row>
     <row r="39">
@@ -973,13 +973,13 @@
         <v>0.12</v>
       </c>
       <c r="B39" t="n">
-        <v>0.04004070675515403</v>
+        <v>0.0590025862750343</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07995929324484596</v>
+        <v>0.0609974137249657</v>
       </c>
       <c r="D39" t="n">
-        <v>66.63274437070498</v>
+        <v>50.83117810413809</v>
       </c>
     </row>
     <row r="40">
@@ -987,13 +987,13 @@
         <v>0.55</v>
       </c>
       <c r="B40" t="n">
-        <v>0.4481637936149012</v>
+        <v>0.4619592734583288</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1018362063850988</v>
+        <v>0.08804072654167128</v>
       </c>
       <c r="D40" t="n">
-        <v>18.51567388819979</v>
+        <v>16.00740482575841</v>
       </c>
     </row>
     <row r="41">
@@ -1001,13 +1001,13 @@
         <v>0.04</v>
       </c>
       <c r="B41" t="n">
-        <v>0.08538332556705452</v>
+        <v>0.07892514277825197</v>
       </c>
       <c r="C41" t="n">
-        <v>0.04538332556705452</v>
+        <v>0.03892514277825197</v>
       </c>
       <c r="D41" t="n">
-        <v>113.4583139176363</v>
+        <v>97.31285694562992</v>
       </c>
     </row>
     <row r="42">
@@ -1015,13 +1015,13 @@
         <v>0.12</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1256627562729365</v>
+        <v>0.1390064817911769</v>
       </c>
       <c r="C42" t="n">
-        <v>0.005662756272936553</v>
+        <v>0.01900648179117687</v>
       </c>
       <c r="D42" t="n">
-        <v>4.718963560780462</v>
+        <v>15.83873482598072</v>
       </c>
     </row>
     <row r="43">
@@ -1029,13 +1029,13 @@
         <v>0.05</v>
       </c>
       <c r="B43" t="n">
-        <v>0.09363706743062783</v>
+        <v>0.1035555979687176</v>
       </c>
       <c r="C43" t="n">
-        <v>0.04363706743062783</v>
+        <v>0.0535555979687176</v>
       </c>
       <c r="D43" t="n">
-        <v>87.27413486125565</v>
+        <v>107.1111959374352</v>
       </c>
     </row>
     <row r="44">
@@ -1043,13 +1043,13 @@
         <v>0.06</v>
       </c>
       <c r="B44" t="n">
-        <v>0.02960374524873832</v>
+        <v>0.02562193328477852</v>
       </c>
       <c r="C44" t="n">
-        <v>0.03039625475126168</v>
+        <v>0.03437806671522148</v>
       </c>
       <c r="D44" t="n">
-        <v>50.66042458543613</v>
+        <v>57.29677785870246</v>
       </c>
     </row>
     <row r="45">
@@ -1057,13 +1057,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0666266680321953</v>
+        <v>0.02408976503645022</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003373331967804705</v>
+        <v>0.04591023496354979</v>
       </c>
       <c r="D45" t="n">
-        <v>4.819045668292435</v>
+        <v>65.58604994792826</v>
       </c>
     </row>
     <row r="46">
@@ -1071,13 +1071,13 @@
         <v>0.4</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1654829188155885</v>
+        <v>0.1467508436464452</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2345170811844115</v>
+        <v>0.2532491563535548</v>
       </c>
       <c r="D46" t="n">
-        <v>58.62927029610287</v>
+        <v>63.31228908838871</v>
       </c>
     </row>
     <row r="47">
@@ -1085,13 +1085,13 @@
         <v>0.03</v>
       </c>
       <c r="B47" t="n">
-        <v>0.05166633173225799</v>
+        <v>0.005625243189142259</v>
       </c>
       <c r="C47" t="n">
-        <v>0.02166633173225799</v>
+        <v>0.02437475681085774</v>
       </c>
       <c r="D47" t="n">
-        <v>72.22110577419329</v>
+        <v>81.24918936952579</v>
       </c>
     </row>
     <row r="48">
@@ -1099,13 +1099,13 @@
         <v>0.32</v>
       </c>
       <c r="B48" t="n">
-        <v>0.3690009187879931</v>
+        <v>0.3449239673269883</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04900091878799312</v>
+        <v>0.02492396732698832</v>
       </c>
       <c r="D48" t="n">
-        <v>15.31278712124785</v>
+        <v>7.788739789683849</v>
       </c>
     </row>
     <row r="49">
@@ -1113,13 +1113,13 @@
         <v>0.62</v>
       </c>
       <c r="B49" t="n">
-        <v>0.4243741584589052</v>
+        <v>0.4017519999719862</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1956258415410947</v>
+        <v>0.2182480000280138</v>
       </c>
       <c r="D49" t="n">
-        <v>31.55255508727335</v>
+        <v>35.201290327099</v>
       </c>
     </row>
     <row r="50">
@@ -1127,13 +1127,13 @@
         <v>0.14</v>
       </c>
       <c r="B50" t="n">
-        <v>0.06051990170240829</v>
+        <v>0.08599269658430131</v>
       </c>
       <c r="C50" t="n">
-        <v>0.07948009829759173</v>
+        <v>0.0540073034156987</v>
       </c>
       <c r="D50" t="n">
-        <v>56.77149878399409</v>
+        <v>38.57664529692764</v>
       </c>
     </row>
     <row r="51">
@@ -1141,13 +1141,13 @@
         <v>0.05</v>
       </c>
       <c r="B51" t="n">
-        <v>0.05278357741023454</v>
+        <v>0.04588020520359742</v>
       </c>
       <c r="C51" t="n">
-        <v>0.002783577410234536</v>
+        <v>0.004119794796402579</v>
       </c>
       <c r="D51" t="n">
-        <v>5.567154820469073</v>
+        <v>8.239589592805158</v>
       </c>
     </row>
     <row r="52">
@@ -1155,13 +1155,13 @@
         <v>0.27</v>
       </c>
       <c r="B52" t="n">
-        <v>0.06907731900372682</v>
+        <v>0.06828527585782823</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2009226809962732</v>
+        <v>0.2017147241421718</v>
       </c>
       <c r="D52" t="n">
-        <v>74.41580777639749</v>
+        <v>74.70915708969325</v>
       </c>
     </row>
     <row r="53">
@@ -1169,13 +1169,13 @@
         <v>0.22</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2364992929766797</v>
+        <v>0.2429334576258479</v>
       </c>
       <c r="C53" t="n">
-        <v>0.01649929297667971</v>
+        <v>0.02293345762584792</v>
       </c>
       <c r="D53" t="n">
-        <v>7.499678625763504</v>
+        <v>10.42429892083996</v>
       </c>
     </row>
     <row r="54">
@@ -1183,13 +1183,13 @@
         <v>0.04</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0589464987410403</v>
+        <v>0.06945187097604</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0189464987410403</v>
+        <v>0.02945187097604</v>
       </c>
       <c r="D54" t="n">
-        <v>47.36624685260074</v>
+        <v>73.6296774401</v>
       </c>
     </row>
     <row r="55">
@@ -1197,13 +1197,13 @@
         <v>0.71</v>
       </c>
       <c r="B55" t="n">
-        <v>0.671573148584542</v>
+        <v>0.6244016788347077</v>
       </c>
       <c r="C55" t="n">
-        <v>0.03842685141545799</v>
+        <v>0.08559832116529231</v>
       </c>
       <c r="D55" t="n">
-        <v>5.412232593726477</v>
+        <v>12.05610157257638</v>
       </c>
     </row>
     <row r="56">
@@ -1211,13 +1211,13 @@
         <v>0.11</v>
       </c>
       <c r="B56" t="n">
-        <v>0.0963878905544211</v>
+        <v>0.09376076049301701</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0136121094455789</v>
+        <v>0.01623923950698299</v>
       </c>
       <c r="D56" t="n">
-        <v>12.37464495052628</v>
+        <v>14.76294500634817</v>
       </c>
     </row>
     <row r="57">
@@ -1225,13 +1225,13 @@
         <v>0.42</v>
       </c>
       <c r="B57" t="n">
-        <v>0.5436083509955673</v>
+        <v>0.498282095580683</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1236083509955673</v>
+        <v>0.07828209558068305</v>
       </c>
       <c r="D57" t="n">
-        <v>29.43055976084935</v>
+        <v>18.63859418587692</v>
       </c>
     </row>
     <row r="58">
@@ -1239,13 +1239,13 @@
         <v>0.97</v>
       </c>
       <c r="B58" t="n">
-        <v>0.9329607969936089</v>
+        <v>0.889791254688155</v>
       </c>
       <c r="C58" t="n">
-        <v>0.03703920300639107</v>
+        <v>0.08020874531184496</v>
       </c>
       <c r="D58" t="n">
-        <v>3.818474536741348</v>
+        <v>8.268942815654121</v>
       </c>
     </row>
     <row r="59">
@@ -1253,13 +1253,13 @@
         <v>0.16</v>
       </c>
       <c r="B59" t="n">
-        <v>0.09001113788707293</v>
+        <v>0.09002398597568229</v>
       </c>
       <c r="C59" t="n">
-        <v>0.06998886211292707</v>
+        <v>0.06997601402431772</v>
       </c>
       <c r="D59" t="n">
-        <v>43.74303882057941</v>
+        <v>43.73500876519857</v>
       </c>
     </row>
     <row r="60">
@@ -1267,13 +1267,13 @@
         <v>0.52</v>
       </c>
       <c r="B60" t="n">
-        <v>0.5632689243962292</v>
+        <v>0.5725791590387087</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0432689243962292</v>
+        <v>0.05257915903870869</v>
       </c>
       <c r="D60" t="n">
-        <v>8.320946999274845</v>
+        <v>10.11137673821321</v>
       </c>
     </row>
     <row r="61">
@@ -1281,13 +1281,13 @@
         <v>0.23</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3461105990549377</v>
+        <v>0.330460615197222</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1161105990549377</v>
+        <v>0.100460615197222</v>
       </c>
       <c r="D61" t="n">
-        <v>50.48286915432075</v>
+        <v>43.67852834661826</v>
       </c>
     </row>
     <row r="62">
@@ -1295,13 +1295,13 @@
         <v>0.13</v>
       </c>
       <c r="B62" t="n">
-        <v>0.09628703546274009</v>
+        <v>0.08083468254559095</v>
       </c>
       <c r="C62" t="n">
-        <v>0.03371296453725992</v>
+        <v>0.04916531745440905</v>
       </c>
       <c r="D62" t="n">
-        <v>25.93304964404609</v>
+        <v>37.81947496493004</v>
       </c>
     </row>
     <row r="63">
@@ -1309,13 +1309,13 @@
         <v>0.02</v>
       </c>
       <c r="B63" t="n">
-        <v>0.04521951447906347</v>
+        <v>0.05592485877381198</v>
       </c>
       <c r="C63" t="n">
-        <v>0.02521951447906347</v>
+        <v>0.03592485877381198</v>
       </c>
       <c r="D63" t="n">
-        <v>126.0975723953174</v>
+        <v>179.6242938690599</v>
       </c>
     </row>
     <row r="64">
@@ -1323,13 +1323,13 @@
         <v>0.02</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1073440673190906</v>
+        <v>0.1290848591110353</v>
       </c>
       <c r="C64" t="n">
-        <v>0.08734406731909063</v>
+        <v>0.1090848591110353</v>
       </c>
       <c r="D64" t="n">
-        <v>436.7203365954531</v>
+        <v>545.4242955551767</v>
       </c>
     </row>
     <row r="65">
@@ -1337,13 +1337,13 @@
         <v>0.96</v>
       </c>
       <c r="B65" t="n">
-        <v>0.5176657445635465</v>
+        <v>0.5047663380679628</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4423342554364534</v>
+        <v>0.4552336619320372</v>
       </c>
       <c r="D65" t="n">
-        <v>46.07648494129724</v>
+        <v>47.42017311792054</v>
       </c>
     </row>
     <row r="66">
@@ -1351,13 +1351,13 @@
         <v>0.04</v>
       </c>
       <c r="B66" t="n">
-        <v>0.05099142550110347</v>
+        <v>0.07091872905835844</v>
       </c>
       <c r="C66" t="n">
-        <v>0.01099142550110347</v>
+        <v>0.03091872905835844</v>
       </c>
       <c r="D66" t="n">
-        <v>27.47856375275868</v>
+        <v>77.2968226458961</v>
       </c>
     </row>
     <row r="67">
@@ -1365,13 +1365,13 @@
         <v>0.12</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1683605677780975</v>
+        <v>0.180284993680674</v>
       </c>
       <c r="C67" t="n">
-        <v>0.04836056777809755</v>
+        <v>0.06028499368067397</v>
       </c>
       <c r="D67" t="n">
-        <v>40.30047314841462</v>
+        <v>50.23749473389498</v>
       </c>
     </row>
     <row r="68">
@@ -1379,13 +1379,13 @@
         <v>0.02</v>
       </c>
       <c r="B68" t="n">
-        <v>0.05664176374590324</v>
+        <v>0.02804482326379892</v>
       </c>
       <c r="C68" t="n">
-        <v>0.03664176374590324</v>
+        <v>0.008044823263798923</v>
       </c>
       <c r="D68" t="n">
-        <v>183.2088187295162</v>
+        <v>40.22411631899461</v>
       </c>
     </row>
     <row r="69">
@@ -1393,13 +1393,13 @@
         <v>0.03</v>
       </c>
       <c r="B69" t="n">
-        <v>0.03884441724548815</v>
+        <v>0.03666387747090832</v>
       </c>
       <c r="C69" t="n">
-        <v>0.008844417245488151</v>
+        <v>0.006663877470908325</v>
       </c>
       <c r="D69" t="n">
-        <v>29.48139081829384</v>
+        <v>22.21292490302775</v>
       </c>
     </row>
     <row r="70">
@@ -1407,13 +1407,13 @@
         <v>0.2</v>
       </c>
       <c r="B70" t="n">
-        <v>0.2376597022431963</v>
+        <v>0.2155356138415881</v>
       </c>
       <c r="C70" t="n">
-        <v>0.03765970224319631</v>
+        <v>0.01553561384158808</v>
       </c>
       <c r="D70" t="n">
-        <v>18.82985112159816</v>
+        <v>7.76780692079404</v>
       </c>
     </row>
     <row r="71">
@@ -1421,13 +1421,13 @@
         <v>0.44</v>
       </c>
       <c r="B71" t="n">
-        <v>0.5813134293659457</v>
+        <v>0.5988405750502955</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1413134293659457</v>
+        <v>0.1588405750502955</v>
       </c>
       <c r="D71" t="n">
-        <v>32.11668849226037</v>
+        <v>36.10013069324899</v>
       </c>
     </row>
     <row r="72">
@@ -1435,13 +1435,13 @@
         <v>0.14</v>
       </c>
       <c r="B72" t="n">
-        <v>0.2629338513267697</v>
+        <v>0.2475364179078831</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1229338513267697</v>
+        <v>0.107536417907883</v>
       </c>
       <c r="D72" t="n">
-        <v>87.8098938048355</v>
+        <v>76.81172707705932</v>
       </c>
     </row>
     <row r="73">
@@ -1449,13 +1449,13 @@
         <v>0.05</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1235193287210818</v>
+        <v>0.146024982292786</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07351932872108184</v>
+        <v>0.09602498229278604</v>
       </c>
       <c r="D73" t="n">
-        <v>147.0386574421637</v>
+        <v>192.0499645855721</v>
       </c>
     </row>
     <row r="74">
@@ -1463,13 +1463,13 @@
         <v>0.2</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1657413135794576</v>
+        <v>0.1613505909454682</v>
       </c>
       <c r="C74" t="n">
-        <v>0.03425868642054242</v>
+        <v>0.03864940905453185</v>
       </c>
       <c r="D74" t="n">
-        <v>17.12934321027121</v>
+        <v>19.32470452726592</v>
       </c>
     </row>
     <row r="75">
@@ -1477,13 +1477,13 @@
         <v>0.89</v>
       </c>
       <c r="B75" t="n">
-        <v>0.9497555414198486</v>
+        <v>0.9296992015123431</v>
       </c>
       <c r="C75" t="n">
-        <v>0.05975554141984862</v>
+        <v>0.03969920151234307</v>
       </c>
       <c r="D75" t="n">
-        <v>6.714105777511081</v>
+        <v>4.46058443958911</v>
       </c>
     </row>
     <row r="76">
@@ -1491,13 +1491,13 @@
         <v>0.09</v>
       </c>
       <c r="B76" t="n">
-        <v>0.2498230365115213</v>
+        <v>0.2239112464130435</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1598230365115213</v>
+        <v>0.1339112464130435</v>
       </c>
       <c r="D76" t="n">
-        <v>177.5811516794681</v>
+        <v>148.7902737922706</v>
       </c>
     </row>
     <row r="77">
@@ -1505,10 +1505,10 @@
         <v>0</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1321169920986985</v>
+        <v>0.08550701461177557</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1321169920986985</v>
+        <v>0.08550701461177557</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1521,13 +1521,13 @@
         <v>0.05</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1591794194949062</v>
+        <v>0.1671399005898182</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1091794194949062</v>
+        <v>0.1171399005898182</v>
       </c>
       <c r="D78" t="n">
-        <v>218.3588389898123</v>
+        <v>234.2798011796364</v>
       </c>
     </row>
     <row r="79">
@@ -1535,13 +1535,13 @@
         <v>0.06</v>
       </c>
       <c r="B79" t="n">
-        <v>0.03425327339086248</v>
+        <v>0.05472480904454508</v>
       </c>
       <c r="C79" t="n">
-        <v>0.02574672660913752</v>
+        <v>0.005275190955454923</v>
       </c>
       <c r="D79" t="n">
-        <v>42.91121101522919</v>
+        <v>8.791984925758205</v>
       </c>
     </row>
     <row r="80">
@@ -1549,13 +1549,13 @@
         <v>0.15</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1784745971192674</v>
+        <v>0.1953006370820144</v>
       </c>
       <c r="C80" t="n">
-        <v>0.02847459711926745</v>
+        <v>0.0453006370820144</v>
       </c>
       <c r="D80" t="n">
-        <v>18.9830647461783</v>
+        <v>30.20042472134293</v>
       </c>
     </row>
     <row r="81">
@@ -1563,13 +1563,13 @@
         <v>0.13</v>
       </c>
       <c r="B81" t="n">
-        <v>0.06292398196694959</v>
+        <v>0.06958412761550525</v>
       </c>
       <c r="C81" t="n">
-        <v>0.06707601803305041</v>
+        <v>0.06041587238449475</v>
       </c>
       <c r="D81" t="n">
-        <v>51.59693694850031</v>
+        <v>46.47374798807288</v>
       </c>
     </row>
     <row r="82">
@@ -1577,13 +1577,13 @@
         <v>1</v>
       </c>
       <c r="B82" t="n">
-        <v>0.566388075086814</v>
+        <v>0.5374959636797502</v>
       </c>
       <c r="C82" t="n">
-        <v>0.433611924913186</v>
+        <v>0.4625040363202498</v>
       </c>
       <c r="D82" t="n">
-        <v>43.3611924913186</v>
+        <v>46.25040363202498</v>
       </c>
     </row>
     <row r="83">
@@ -1591,13 +1591,13 @@
         <v>0.06</v>
       </c>
       <c r="B83" t="n">
-        <v>0.07469943127640899</v>
+        <v>0.0802601240972694</v>
       </c>
       <c r="C83" t="n">
-        <v>0.01469943127640899</v>
+        <v>0.02026012409726941</v>
       </c>
       <c r="D83" t="n">
-        <v>24.49905212734832</v>
+        <v>33.76687349544901</v>
       </c>
     </row>
     <row r="84">
@@ -1605,13 +1605,13 @@
         <v>0.22</v>
       </c>
       <c r="B84" t="n">
-        <v>0.2741864049423035</v>
+        <v>0.2546554927915169</v>
       </c>
       <c r="C84" t="n">
-        <v>0.05418640494230345</v>
+        <v>0.03465549279151689</v>
       </c>
       <c r="D84" t="n">
-        <v>24.63018406468339</v>
+        <v>15.75249672341677</v>
       </c>
     </row>
     <row r="85">
@@ -1619,13 +1619,13 @@
         <v>0.04</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0936551100249976</v>
+        <v>0.09961166054616172</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0536551100249976</v>
+        <v>0.05961166054616172</v>
       </c>
       <c r="D85" t="n">
-        <v>134.137775062494</v>
+        <v>149.0291513654043</v>
       </c>
     </row>
     <row r="86">
@@ -1633,13 +1633,13 @@
         <v>0.13</v>
       </c>
       <c r="B86" t="n">
-        <v>0.2012848020010106</v>
+        <v>0.2318215950420077</v>
       </c>
       <c r="C86" t="n">
-        <v>0.07128480200101062</v>
+        <v>0.1018215950420077</v>
       </c>
       <c r="D86" t="n">
-        <v>54.83446307770047</v>
+        <v>78.32430387846748</v>
       </c>
     </row>
     <row r="87">
@@ -1647,13 +1647,13 @@
         <v>0.12</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2928562813918504</v>
+        <v>0.3047689287754464</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1728562813918504</v>
+        <v>0.1847689287754464</v>
       </c>
       <c r="D87" t="n">
-        <v>144.0469011598753</v>
+        <v>153.974107312872</v>
       </c>
     </row>
     <row r="88">
@@ -1661,13 +1661,13 @@
         <v>0.12</v>
       </c>
       <c r="B88" t="n">
-        <v>0.2925641979302527</v>
+        <v>0.3226032074128328</v>
       </c>
       <c r="C88" t="n">
-        <v>0.1725641979302527</v>
+        <v>0.2026032074128328</v>
       </c>
       <c r="D88" t="n">
-        <v>143.8034982752106</v>
+        <v>168.8360061773606</v>
       </c>
     </row>
     <row r="89">
@@ -1675,13 +1675,13 @@
         <v>0.08</v>
       </c>
       <c r="B89" t="n">
-        <v>0.08749996710186414</v>
+        <v>0.09022492339297583</v>
       </c>
       <c r="C89" t="n">
-        <v>0.007499967101864138</v>
+        <v>0.01022492339297583</v>
       </c>
       <c r="D89" t="n">
-        <v>9.374958877330172</v>
+        <v>12.78115424121979</v>
       </c>
     </row>
     <row r="90">
@@ -1689,13 +1689,13 @@
         <v>0.05</v>
       </c>
       <c r="B90" t="n">
-        <v>0.1326031854267593</v>
+        <v>0.165963505929016</v>
       </c>
       <c r="C90" t="n">
-        <v>0.08260318542675925</v>
+        <v>0.115963505929016</v>
       </c>
       <c r="D90" t="n">
-        <v>165.2063708535185</v>
+        <v>231.9270118580321</v>
       </c>
     </row>
     <row r="91">
@@ -1703,13 +1703,13 @@
         <v>0.08</v>
       </c>
       <c r="B91" t="n">
-        <v>0.1645154305567861</v>
+        <v>0.1695653522448999</v>
       </c>
       <c r="C91" t="n">
-        <v>0.08451543055678608</v>
+        <v>0.08956535224489988</v>
       </c>
       <c r="D91" t="n">
-        <v>105.6442881959826</v>
+        <v>111.9566903061249</v>
       </c>
     </row>
     <row r="92">
@@ -1717,13 +1717,13 @@
         <v>0.54</v>
       </c>
       <c r="B92" t="n">
-        <v>0.2623312815346532</v>
+        <v>0.2781432519757013</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2776687184653469</v>
+        <v>0.2618567480242987</v>
       </c>
       <c r="D92" t="n">
-        <v>51.42013304913831</v>
+        <v>48.49199037487013</v>
       </c>
     </row>
     <row r="93">
@@ -1731,13 +1731,13 @@
         <v>0.32</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3470416152980563</v>
+        <v>0.3541073958931737</v>
       </c>
       <c r="C93" t="n">
-        <v>0.02704161529805632</v>
+        <v>0.03410739589317374</v>
       </c>
       <c r="D93" t="n">
-        <v>8.4505047806426</v>
+        <v>10.65856121661679</v>
       </c>
     </row>
     <row r="94">
@@ -1745,13 +1745,13 @@
         <v>0.11</v>
       </c>
       <c r="B94" t="n">
-        <v>0.08413675436107959</v>
+        <v>0.08690060743464773</v>
       </c>
       <c r="C94" t="n">
-        <v>0.02586324563892041</v>
+        <v>0.02309939256535228</v>
       </c>
       <c r="D94" t="n">
-        <v>23.51204148992765</v>
+        <v>20.99944778668389</v>
       </c>
     </row>
     <row r="95">
@@ -1759,13 +1759,13 @@
         <v>0.18</v>
       </c>
       <c r="B95" t="n">
-        <v>0.07399114143119312</v>
+        <v>0.07854337985018917</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1060088585688069</v>
+        <v>0.1014566201498108</v>
       </c>
       <c r="D95" t="n">
-        <v>58.89381031600382</v>
+        <v>56.36478897211713</v>
       </c>
     </row>
     <row r="96">
@@ -1773,13 +1773,13 @@
         <v>0.29</v>
       </c>
       <c r="B96" t="n">
-        <v>0.3524855611377027</v>
+        <v>0.3592491612845603</v>
       </c>
       <c r="C96" t="n">
-        <v>0.06248556113770271</v>
+        <v>0.06924916128456032</v>
       </c>
       <c r="D96" t="n">
-        <v>21.54674521989749</v>
+        <v>23.87902113260701</v>
       </c>
     </row>
     <row r="97">
@@ -1787,13 +1787,13 @@
         <v>0.53</v>
       </c>
       <c r="B97" t="n">
-        <v>0.2473250805168615</v>
+        <v>0.2674302042820439</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2826749194831385</v>
+        <v>0.2625697957179561</v>
       </c>
       <c r="D97" t="n">
-        <v>53.33489046851669</v>
+        <v>49.54147089018039</v>
       </c>
     </row>
     <row r="98">
@@ -1801,13 +1801,13 @@
         <v>0.08</v>
       </c>
       <c r="B98" t="n">
-        <v>0.1196354775791887</v>
+        <v>0.1329224599656843</v>
       </c>
       <c r="C98" t="n">
-        <v>0.03963547757918869</v>
+        <v>0.0529224599656843</v>
       </c>
       <c r="D98" t="n">
-        <v>49.54434697398585</v>
+        <v>66.15307495710537</v>
       </c>
     </row>
     <row r="99">
@@ -1815,13 +1815,13 @@
         <v>0.18</v>
       </c>
       <c r="B99" t="n">
-        <v>0.5330419545670378</v>
+        <v>0.5646185178035109</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3530419545670379</v>
+        <v>0.3846185178035109</v>
       </c>
       <c r="D99" t="n">
-        <v>196.1344192039099</v>
+        <v>213.6769543352839</v>
       </c>
     </row>
     <row r="100">
@@ -1829,13 +1829,13 @@
         <v>0.19</v>
       </c>
       <c r="B100" t="n">
-        <v>0.3099159017336875</v>
+        <v>0.2737443932448845</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1199159017336875</v>
+        <v>0.08374439324488453</v>
       </c>
       <c r="D100" t="n">
-        <v>63.11363249141449</v>
+        <v>44.07599644467607</v>
       </c>
     </row>
     <row r="101">
@@ -1843,13 +1843,13 @@
         <v>0.01</v>
       </c>
       <c r="B101" t="n">
-        <v>0.03098188615321851</v>
+        <v>0.0273712800031875</v>
       </c>
       <c r="C101" t="n">
-        <v>0.02098188615321851</v>
+        <v>0.0173712800031875</v>
       </c>
       <c r="D101" t="n">
-        <v>209.818861532185</v>
+        <v>173.712800031875</v>
       </c>
     </row>
     <row r="102">
@@ -1857,13 +1857,13 @@
         <v>0.11</v>
       </c>
       <c r="B102" t="n">
-        <v>0.1041396761018214</v>
+        <v>0.1094458539704654</v>
       </c>
       <c r="C102" t="n">
-        <v>0.005860323898178602</v>
+        <v>0.000554146029534644</v>
       </c>
       <c r="D102" t="n">
-        <v>5.327567180162365</v>
+        <v>0.5037691177587672</v>
       </c>
     </row>
     <row r="103">
@@ -1871,13 +1871,13 @@
         <v>0.11</v>
       </c>
       <c r="B103" t="n">
-        <v>0.2019861156992477</v>
+        <v>0.2138336794925674</v>
       </c>
       <c r="C103" t="n">
-        <v>0.09198611569924768</v>
+        <v>0.1038336794925674</v>
       </c>
       <c r="D103" t="n">
-        <v>83.62374154477061</v>
+        <v>94.39425408415221</v>
       </c>
     </row>
     <row r="104">
@@ -1885,13 +1885,13 @@
         <v>0.63</v>
       </c>
       <c r="B104" t="n">
-        <v>0.4476855247430759</v>
+        <v>0.4912858692682294</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1823144752569241</v>
+        <v>0.1387141307317706</v>
       </c>
       <c r="D104" t="n">
-        <v>28.93880559633716</v>
+        <v>22.01811598916994</v>
       </c>
     </row>
     <row r="105">
@@ -1899,13 +1899,13 @@
         <v>0.08</v>
       </c>
       <c r="B105" t="n">
-        <v>0.1333880522765217</v>
+        <v>0.1331557173103519</v>
       </c>
       <c r="C105" t="n">
-        <v>0.05338805227652167</v>
+        <v>0.05315571731035192</v>
       </c>
       <c r="D105" t="n">
-        <v>66.73506534565209</v>
+        <v>66.4446466379399</v>
       </c>
     </row>
     <row r="106">
@@ -1913,13 +1913,13 @@
         <v>0.01</v>
       </c>
       <c r="B106" t="n">
-        <v>0.05940610065893182</v>
+        <v>0.03529269487925374</v>
       </c>
       <c r="C106" t="n">
-        <v>0.04940610065893181</v>
+        <v>0.02529269487925374</v>
       </c>
       <c r="D106" t="n">
-        <v>494.0610065893181</v>
+        <v>252.9269487925374</v>
       </c>
     </row>
     <row r="107">
@@ -1927,13 +1927,13 @@
         <v>0.18</v>
       </c>
       <c r="B107" t="n">
-        <v>0.2221792549436552</v>
+        <v>0.2193564724064351</v>
       </c>
       <c r="C107" t="n">
-        <v>0.04217925494365521</v>
+        <v>0.03935647240643508</v>
       </c>
       <c r="D107" t="n">
-        <v>23.43291941314178</v>
+        <v>21.86470689246394</v>
       </c>
     </row>
     <row r="108">
@@ -1941,13 +1941,13 @@
         <v>0.03</v>
       </c>
       <c r="B108" t="n">
-        <v>0.07206305075440589</v>
+        <v>0.006626422957172862</v>
       </c>
       <c r="C108" t="n">
-        <v>0.04206305075440589</v>
+        <v>0.02337357704282714</v>
       </c>
       <c r="D108" t="n">
-        <v>140.210169181353</v>
+        <v>77.91192347609046</v>
       </c>
     </row>
     <row r="109">
@@ -1955,13 +1955,13 @@
         <v>0.11</v>
       </c>
       <c r="B109" t="n">
-        <v>0.141955302475717</v>
+        <v>0.1335209083090815</v>
       </c>
       <c r="C109" t="n">
-        <v>0.03195530247571703</v>
+        <v>0.02352090830908148</v>
       </c>
       <c r="D109" t="n">
-        <v>29.05027497792457</v>
+        <v>21.3826439173468</v>
       </c>
     </row>
     <row r="110">
@@ -1969,13 +1969,13 @@
         <v>0.02</v>
       </c>
       <c r="B110" t="n">
-        <v>0.06173730100501151</v>
+        <v>0.0432849674334112</v>
       </c>
       <c r="C110" t="n">
-        <v>0.04173730100501151</v>
+        <v>0.0232849674334112</v>
       </c>
       <c r="D110" t="n">
-        <v>208.6865050250575</v>
+        <v>116.424837167056</v>
       </c>
     </row>
     <row r="111">
@@ -1983,13 +1983,13 @@
         <v>0.76</v>
       </c>
       <c r="B111" t="n">
-        <v>0.5090449937303766</v>
+        <v>0.4933633591343349</v>
       </c>
       <c r="C111" t="n">
-        <v>0.2509550062696234</v>
+        <v>0.2666366408656651</v>
       </c>
       <c r="D111" t="n">
-        <v>33.02039556179255</v>
+        <v>35.08376853495594</v>
       </c>
     </row>
     <row r="112">
@@ -1997,13 +1997,13 @@
         <v>0.04</v>
       </c>
       <c r="B112" t="n">
-        <v>0.07198443302699276</v>
+        <v>0.07714081251282473</v>
       </c>
       <c r="C112" t="n">
-        <v>0.03198443302699275</v>
+        <v>0.03714081251282473</v>
       </c>
       <c r="D112" t="n">
-        <v>79.9610825674819</v>
+        <v>92.85203128206182</v>
       </c>
     </row>
     <row r="113">
@@ -2011,13 +2011,13 @@
         <v>0.02</v>
       </c>
       <c r="B113" t="n">
-        <v>0.04803609023615329</v>
+        <v>0.02247267147073734</v>
       </c>
       <c r="C113" t="n">
-        <v>0.02803609023615329</v>
+        <v>0.002472671470737337</v>
       </c>
       <c r="D113" t="n">
-        <v>140.1804511807665</v>
+        <v>12.36335735368669</v>
       </c>
     </row>
     <row r="114">
@@ -2025,13 +2025,13 @@
         <v>0.48</v>
       </c>
       <c r="B114" t="n">
-        <v>0.383333229112273</v>
+        <v>0.3493262622280061</v>
       </c>
       <c r="C114" t="n">
-        <v>0.09666677088772696</v>
+        <v>0.1306737377719939</v>
       </c>
       <c r="D114" t="n">
-        <v>20.13891060160978</v>
+        <v>27.22369536916539</v>
       </c>
     </row>
     <row r="115">
@@ -2039,13 +2039,13 @@
         <v>0.31</v>
       </c>
       <c r="B115" t="n">
-        <v>0.4798064393871604</v>
+        <v>0.4261783681355456</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1698064393871604</v>
+        <v>0.1161783681355456</v>
       </c>
       <c r="D115" t="n">
-        <v>54.77627077005174</v>
+        <v>37.47689294695019</v>
       </c>
     </row>
     <row r="116">
@@ -2053,13 +2053,13 @@
         <v>0.13</v>
       </c>
       <c r="B116" t="n">
-        <v>0.06313628129133253</v>
+        <v>0.07995782511262861</v>
       </c>
       <c r="C116" t="n">
-        <v>0.06686371870866747</v>
+        <v>0.05004217488737139</v>
       </c>
       <c r="D116" t="n">
-        <v>51.43362977589806</v>
+        <v>38.49398068259337</v>
       </c>
     </row>
     <row r="117">
@@ -2067,13 +2067,13 @@
         <v>0.02</v>
       </c>
       <c r="B117" t="n">
-        <v>0.02311793650561378</v>
+        <v>0.006833111044371731</v>
       </c>
       <c r="C117" t="n">
-        <v>0.003117936505613778</v>
+        <v>0.01316688895562827</v>
       </c>
       <c r="D117" t="n">
-        <v>15.58968252806889</v>
+        <v>65.83444477814135</v>
       </c>
     </row>
     <row r="118">
@@ -2081,13 +2081,13 @@
         <v>0.04</v>
       </c>
       <c r="B118" t="n">
-        <v>0.1024881120856631</v>
+        <v>0.1128569405479448</v>
       </c>
       <c r="C118" t="n">
-        <v>0.06248811208566311</v>
+        <v>0.07285694054794481</v>
       </c>
       <c r="D118" t="n">
-        <v>156.2202802141578</v>
+        <v>182.142351369862</v>
       </c>
     </row>
     <row r="119">
@@ -2095,13 +2095,13 @@
         <v>0.14</v>
       </c>
       <c r="B119" t="n">
-        <v>0.09714561097934327</v>
+        <v>0.139768999881306</v>
       </c>
       <c r="C119" t="n">
-        <v>0.04285438902065675</v>
+        <v>0.0002310001186940358</v>
       </c>
       <c r="D119" t="n">
-        <v>30.61027787189767</v>
+        <v>0.1650000847814541</v>
       </c>
     </row>
     <row r="120">
@@ -2109,13 +2109,13 @@
         <v>0.12</v>
       </c>
       <c r="B120" t="n">
-        <v>0.1718508077463241</v>
+        <v>0.1824692268046916</v>
       </c>
       <c r="C120" t="n">
-        <v>0.05185080774632406</v>
+        <v>0.06246922680469158</v>
       </c>
       <c r="D120" t="n">
-        <v>43.20900645527005</v>
+        <v>52.05768900390966</v>
       </c>
     </row>
     <row r="121">
@@ -2123,13 +2123,13 @@
         <v>0.16</v>
       </c>
       <c r="B121" t="n">
-        <v>0.5435116755738444</v>
+        <v>0.5150792374459334</v>
       </c>
       <c r="C121" t="n">
-        <v>0.3835116755738444</v>
+        <v>0.3550792374459334</v>
       </c>
       <c r="D121" t="n">
-        <v>239.6947972336527</v>
+        <v>221.9245234037084</v>
       </c>
     </row>
     <row r="122">
@@ -2137,13 +2137,13 @@
         <v>0.09</v>
       </c>
       <c r="B122" t="n">
-        <v>0.2056281639219332</v>
+        <v>0.2201367301563623</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1156281639219332</v>
+        <v>0.1301367301563623</v>
       </c>
       <c r="D122" t="n">
-        <v>128.4757376910369</v>
+        <v>144.5963668404026</v>
       </c>
     </row>
     <row r="123">
@@ -2151,13 +2151,13 @@
         <v>0.66</v>
       </c>
       <c r="B123" t="n">
-        <v>0.4695410952413923</v>
+        <v>0.3958367926817789</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1904589047586078</v>
+        <v>0.2641632073182211</v>
       </c>
       <c r="D123" t="n">
-        <v>28.85740981191027</v>
+        <v>40.02472838154866</v>
       </c>
     </row>
     <row r="124">
@@ -2165,13 +2165,13 @@
         <v>0.06</v>
       </c>
       <c r="B124" t="n">
-        <v>0.1035326097200108</v>
+        <v>0.09312504957865558</v>
       </c>
       <c r="C124" t="n">
-        <v>0.04353260972001077</v>
+        <v>0.03312504957865559</v>
       </c>
       <c r="D124" t="n">
-        <v>72.55434953335129</v>
+        <v>55.20841596442598</v>
       </c>
     </row>
     <row r="125">
@@ -2179,13 +2179,13 @@
         <v>0.06</v>
       </c>
       <c r="B125" t="n">
-        <v>0.09058081211931535</v>
+        <v>0.0929199154457544</v>
       </c>
       <c r="C125" t="n">
-        <v>0.03058081211931535</v>
+        <v>0.0329199154457544</v>
       </c>
       <c r="D125" t="n">
-        <v>50.96802019885892</v>
+        <v>54.866525742924</v>
       </c>
     </row>
     <row r="126">
@@ -2193,13 +2193,13 @@
         <v>0.53</v>
       </c>
       <c r="B126" t="n">
-        <v>0.3874101414151693</v>
+        <v>0.412874012870082</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1425898585848308</v>
+        <v>0.117125987129918</v>
       </c>
       <c r="D126" t="n">
-        <v>26.90374690279825</v>
+        <v>22.09924285470151</v>
       </c>
     </row>
     <row r="127">
@@ -2207,13 +2207,13 @@
         <v>0.02</v>
       </c>
       <c r="B127" t="n">
-        <v>0.05291958087493531</v>
+        <v>0.04610164161762498</v>
       </c>
       <c r="C127" t="n">
-        <v>0.03291958087493531</v>
+        <v>0.02610164161762498</v>
       </c>
       <c r="D127" t="n">
-        <v>164.5979043746765</v>
+        <v>130.5082080881249</v>
       </c>
     </row>
     <row r="128">
@@ -2221,13 +2221,13 @@
         <v>0.15</v>
       </c>
       <c r="B128" t="n">
-        <v>0.1759716056033592</v>
+        <v>0.1810056070892936</v>
       </c>
       <c r="C128" t="n">
-        <v>0.02597160560335918</v>
+        <v>0.03100560708929365</v>
       </c>
       <c r="D128" t="n">
-        <v>17.31440373557279</v>
+        <v>20.67040472619577</v>
       </c>
     </row>
     <row r="129">
@@ -2235,13 +2235,13 @@
         <v>0.12</v>
       </c>
       <c r="B129" t="n">
-        <v>0.1352568261389676</v>
+        <v>0.1608580305745378</v>
       </c>
       <c r="C129" t="n">
-        <v>0.01525682613896756</v>
+        <v>0.04085803057453785</v>
       </c>
       <c r="D129" t="n">
-        <v>12.71402178247297</v>
+        <v>34.04835881211488</v>
       </c>
     </row>
     <row r="130">
@@ -2249,13 +2249,13 @@
         <v>0.02</v>
       </c>
       <c r="B130" t="n">
-        <v>0.06545492542652864</v>
+        <v>0.02331920695693968</v>
       </c>
       <c r="C130" t="n">
-        <v>0.04545492542652864</v>
+        <v>0.003319206956939675</v>
       </c>
       <c r="D130" t="n">
-        <v>227.2746271326432</v>
+        <v>16.59603478469838</v>
       </c>
     </row>
     <row r="131">
@@ -2263,13 +2263,13 @@
         <v>0.23</v>
       </c>
       <c r="B131" t="n">
-        <v>0.134820442427919</v>
+        <v>0.1417152690304115</v>
       </c>
       <c r="C131" t="n">
-        <v>0.09517955757208099</v>
+        <v>0.08828473096958847</v>
       </c>
       <c r="D131" t="n">
-        <v>41.38241633568739</v>
+        <v>38.38466563895151</v>
       </c>
     </row>
     <row r="132">
@@ -2277,13 +2277,13 @@
         <v>0.33</v>
       </c>
       <c r="B132" t="n">
-        <v>0.3968126437342415</v>
+        <v>0.400263516500841</v>
       </c>
       <c r="C132" t="n">
-        <v>0.06681264373424151</v>
+        <v>0.07026351650084095</v>
       </c>
       <c r="D132" t="n">
-        <v>20.24625567704288</v>
+        <v>21.29197469722453</v>
       </c>
     </row>
     <row r="133">
@@ -2291,13 +2291,13 @@
         <v>0.05</v>
       </c>
       <c r="B133" t="n">
-        <v>0.1049500284875063</v>
+        <v>0.1201571046535065</v>
       </c>
       <c r="C133" t="n">
-        <v>0.05495002848750634</v>
+        <v>0.07015710465350654</v>
       </c>
       <c r="D133" t="n">
-        <v>109.9000569750127</v>
+        <v>140.3142093070131</v>
       </c>
     </row>
     <row r="134">
@@ -2305,13 +2305,13 @@
         <v>0.03</v>
       </c>
       <c r="B134" t="n">
-        <v>0.05246302818880344</v>
+        <v>-0.004764322802398635</v>
       </c>
       <c r="C134" t="n">
-        <v>0.02246302818880344</v>
+        <v>0.03476432280239863</v>
       </c>
       <c r="D134" t="n">
-        <v>74.8767606293448</v>
+        <v>115.8810760079954</v>
       </c>
     </row>
     <row r="135">
@@ -2319,13 +2319,13 @@
         <v>0.19</v>
       </c>
       <c r="B135" t="n">
-        <v>0.07098863357787355</v>
+        <v>0.07115259309639338</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1190113664221265</v>
+        <v>0.1188474069036066</v>
       </c>
       <c r="D135" t="n">
-        <v>62.6375612748034</v>
+        <v>62.55126679137191</v>
       </c>
     </row>
     <row r="136">
@@ -2333,13 +2333,13 @@
         <v>0.25</v>
       </c>
       <c r="B136" t="n">
-        <v>0.5111429672829686</v>
+        <v>0.565578871368584</v>
       </c>
       <c r="C136" t="n">
-        <v>0.2611429672829686</v>
+        <v>0.315578871368584</v>
       </c>
       <c r="D136" t="n">
-        <v>104.4571869131874</v>
+        <v>126.2315485474336</v>
       </c>
     </row>
     <row r="137">
@@ -2347,13 +2347,13 @@
         <v>0.35</v>
       </c>
       <c r="B137" t="n">
-        <v>0.2465808574473207</v>
+        <v>0.2451545986222325</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1034191425526793</v>
+        <v>0.1048454013777675</v>
       </c>
       <c r="D137" t="n">
-        <v>29.54832644362266</v>
+        <v>29.95582896507642</v>
       </c>
     </row>
     <row r="138">
@@ -2361,13 +2361,13 @@
         <v>0.31</v>
       </c>
       <c r="B138" t="n">
-        <v>0.3981992471881466</v>
+        <v>0.3867793742399409</v>
       </c>
       <c r="C138" t="n">
-        <v>0.08819924718814659</v>
+        <v>0.07677937423994091</v>
       </c>
       <c r="D138" t="n">
-        <v>28.45137006069245</v>
+        <v>24.76754007740029</v>
       </c>
     </row>
     <row r="139">
@@ -2375,13 +2375,13 @@
         <v>0.29</v>
       </c>
       <c r="B139" t="n">
-        <v>0.2809376142311705</v>
+        <v>0.2833639899064466</v>
       </c>
       <c r="C139" t="n">
-        <v>0.009062385768829506</v>
+        <v>0.006636010093553357</v>
       </c>
       <c r="D139" t="n">
-        <v>3.124960609941209</v>
+        <v>2.288279342604606</v>
       </c>
     </row>
     <row r="140">
@@ -2389,13 +2389,13 @@
         <v>0.42</v>
       </c>
       <c r="B140" t="n">
-        <v>0.3442469784580634</v>
+        <v>0.3243827111874659</v>
       </c>
       <c r="C140" t="n">
-        <v>0.07575302154193658</v>
+        <v>0.09561728881253412</v>
       </c>
       <c r="D140" t="n">
-        <v>18.03643370046109</v>
+        <v>22.76602114584146</v>
       </c>
     </row>
     <row r="141">
@@ -2403,13 +2403,13 @@
         <v>0.06</v>
       </c>
       <c r="B141" t="n">
-        <v>0.07596294571020545</v>
+        <v>0.07216596907930561</v>
       </c>
       <c r="C141" t="n">
-        <v>0.01596294571020546</v>
+        <v>0.01216596907930562</v>
       </c>
       <c r="D141" t="n">
-        <v>26.60490951700909</v>
+        <v>20.27661513217603</v>
       </c>
     </row>
     <row r="142">
@@ -2417,13 +2417,13 @@
         <v>0.1</v>
       </c>
       <c r="B142" t="n">
-        <v>0.09422594336041645</v>
+        <v>0.1048019492997561</v>
       </c>
       <c r="C142" t="n">
-        <v>0.005774056639583552</v>
+        <v>0.004801949299756109</v>
       </c>
       <c r="D142" t="n">
-        <v>5.774056639583552</v>
+        <v>4.801949299756108</v>
       </c>
     </row>
     <row r="143">
@@ -2431,13 +2431,13 @@
         <v>0.58</v>
       </c>
       <c r="B143" t="n">
-        <v>0.3715738815252824</v>
+        <v>0.3706647897356024</v>
       </c>
       <c r="C143" t="n">
-        <v>0.2084261184747176</v>
+        <v>0.2093352102643976</v>
       </c>
       <c r="D143" t="n">
-        <v>35.93553766805476</v>
+        <v>36.0922776317927</v>
       </c>
     </row>
     <row r="144">
@@ -2445,13 +2445,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B144" t="n">
-        <v>0.2121268568103175</v>
+        <v>0.204441034049744</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1421268568103175</v>
+        <v>0.1344410340497439</v>
       </c>
       <c r="D144" t="n">
-        <v>203.0383668718821</v>
+        <v>192.0586200710628</v>
       </c>
     </row>
     <row r="145">
@@ -2459,13 +2459,13 @@
         <v>0.49</v>
       </c>
       <c r="B145" t="n">
-        <v>0.3435630921143072</v>
+        <v>0.3334253386274262</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1464369078856927</v>
+        <v>0.1565746613725738</v>
       </c>
       <c r="D145" t="n">
-        <v>29.88508324197811</v>
+        <v>31.95401252501506</v>
       </c>
     </row>
     <row r="146">
@@ -2473,13 +2473,13 @@
         <v>0.14</v>
       </c>
       <c r="B146" t="n">
-        <v>0.1581825555038856</v>
+        <v>0.1785091504292814</v>
       </c>
       <c r="C146" t="n">
-        <v>0.01818255550388559</v>
+        <v>0.03850915042928144</v>
       </c>
       <c r="D146" t="n">
-        <v>12.98753964563256</v>
+        <v>27.50653602091531</v>
       </c>
     </row>
     <row r="147">
@@ -2487,13 +2487,13 @@
         <v>0.11</v>
       </c>
       <c r="B147" t="n">
-        <v>0.2580547875136566</v>
+        <v>0.2195118695442156</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1480547875136566</v>
+        <v>0.1095118695442156</v>
       </c>
       <c r="D147" t="n">
-        <v>134.5952613760515</v>
+        <v>99.55624504019603</v>
       </c>
     </row>
     <row r="148">
@@ -2501,13 +2501,13 @@
         <v>0.22</v>
       </c>
       <c r="B148" t="n">
-        <v>0.1873627139368721</v>
+        <v>0.2010409071604937</v>
       </c>
       <c r="C148" t="n">
-        <v>0.03263728606312791</v>
+        <v>0.01895909283950634</v>
       </c>
       <c r="D148" t="n">
-        <v>14.8351300286945</v>
+        <v>8.61776947250288</v>
       </c>
     </row>
     <row r="149">
@@ -2515,13 +2515,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B149" t="n">
-        <v>0.08985640628549851</v>
+        <v>0.1048562817934692</v>
       </c>
       <c r="C149" t="n">
-        <v>0.01985640628549851</v>
+        <v>0.03485628179346922</v>
       </c>
       <c r="D149" t="n">
-        <v>28.36629469356929</v>
+        <v>49.7946882763846</v>
       </c>
     </row>
     <row r="150">
@@ -2529,13 +2529,13 @@
         <v>0.13</v>
       </c>
       <c r="B150" t="n">
-        <v>0.1287152118533001</v>
+        <v>0.142647083542037</v>
       </c>
       <c r="C150" t="n">
-        <v>0.001284788146699856</v>
+        <v>0.01264708354203697</v>
       </c>
       <c r="D150" t="n">
-        <v>0.9882985743845043</v>
+        <v>9.728525801566903</v>
       </c>
     </row>
     <row r="151">
@@ -2543,13 +2543,13 @@
         <v>0.4</v>
       </c>
       <c r="B151" t="n">
-        <v>0.3794661093035757</v>
+        <v>0.3049705814798394</v>
       </c>
       <c r="C151" t="n">
-        <v>0.02053389069642436</v>
+        <v>0.09502941852016067</v>
       </c>
       <c r="D151" t="n">
-        <v>5.13347267410609</v>
+        <v>23.75735463004017</v>
       </c>
     </row>
     <row r="152">
@@ -2557,13 +2557,13 @@
         <v>0.06</v>
       </c>
       <c r="B152" t="n">
-        <v>0.06410386655473332</v>
+        <v>0.04793761600864938</v>
       </c>
       <c r="C152" t="n">
-        <v>0.004103866554733326</v>
+        <v>0.01206238399135062</v>
       </c>
       <c r="D152" t="n">
-        <v>6.839777591222211</v>
+        <v>20.10397331891771</v>
       </c>
     </row>
     <row r="153">
@@ -2571,13 +2571,13 @@
         <v>0.27</v>
       </c>
       <c r="B153" t="n">
-        <v>0.1480588683694677</v>
+        <v>0.1494064742770298</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1219411316305323</v>
+        <v>0.1205935257229702</v>
       </c>
       <c r="D153" t="n">
-        <v>45.16338208538232</v>
+        <v>44.66426878628526</v>
       </c>
     </row>
     <row r="154">
@@ -2585,13 +2585,13 @@
         <v>0.06</v>
       </c>
       <c r="B154" t="n">
-        <v>0.07759331461670205</v>
+        <v>0.06325161516186578</v>
       </c>
       <c r="C154" t="n">
-        <v>0.01759331461670205</v>
+        <v>0.003251615161865784</v>
       </c>
       <c r="D154" t="n">
-        <v>29.32219102783675</v>
+        <v>5.41935860310964</v>
       </c>
     </row>
     <row r="155">
@@ -2599,13 +2599,13 @@
         <v>0.16</v>
       </c>
       <c r="B155" t="n">
-        <v>0.08332679651576436</v>
+        <v>0.1000632967512052</v>
       </c>
       <c r="C155" t="n">
-        <v>0.07667320348423565</v>
+        <v>0.05993670324879483</v>
       </c>
       <c r="D155" t="n">
-        <v>47.92075217764728</v>
+        <v>37.46043953049676</v>
       </c>
     </row>
     <row r="156">
@@ -2613,13 +2613,13 @@
         <v>0.1</v>
       </c>
       <c r="B156" t="n">
-        <v>0.11725992071618</v>
+        <v>0.1314726833124737</v>
       </c>
       <c r="C156" t="n">
-        <v>0.01725992071617996</v>
+        <v>0.03147268331247374</v>
       </c>
       <c r="D156" t="n">
-        <v>17.25992071617996</v>
+        <v>31.47268331247374</v>
       </c>
     </row>
     <row r="157">
@@ -2627,13 +2627,13 @@
         <v>0.15</v>
       </c>
       <c r="B157" t="n">
-        <v>0.1894590338462201</v>
+        <v>0.2122564251729057</v>
       </c>
       <c r="C157" t="n">
-        <v>0.03945903384622015</v>
+        <v>0.06225642517290567</v>
       </c>
       <c r="D157" t="n">
-        <v>26.30602256414677</v>
+        <v>41.50428344860378</v>
       </c>
     </row>
     <row r="158">
@@ -2641,13 +2641,13 @@
         <v>1</v>
       </c>
       <c r="B158" t="n">
-        <v>0.5166587327639169</v>
+        <v>0.5458074791860442</v>
       </c>
       <c r="C158" t="n">
-        <v>0.4833412672360831</v>
+        <v>0.4541925208139558</v>
       </c>
       <c r="D158" t="n">
-        <v>48.33412672360831</v>
+        <v>45.41925208139558</v>
       </c>
     </row>
     <row r="159">
@@ -2655,13 +2655,13 @@
         <v>0.18</v>
       </c>
       <c r="B159" t="n">
-        <v>0.3733239727406787</v>
+        <v>0.3023859256650859</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1933239727406787</v>
+        <v>0.1223859256650859</v>
       </c>
       <c r="D159" t="n">
-        <v>107.4022070781548</v>
+        <v>67.99218092504772</v>
       </c>
     </row>
     <row r="160">
@@ -2669,13 +2669,13 @@
         <v>0.04</v>
       </c>
       <c r="B160" t="n">
-        <v>0.07503334229230663</v>
+        <v>0.08530197017011387</v>
       </c>
       <c r="C160" t="n">
-        <v>0.03503334229230663</v>
+        <v>0.04530197017011387</v>
       </c>
       <c r="D160" t="n">
-        <v>87.58335573076657</v>
+        <v>113.2549254252847</v>
       </c>
     </row>
     <row r="161">
@@ -2683,13 +2683,13 @@
         <v>0.4</v>
       </c>
       <c r="B161" t="n">
-        <v>0.5688782302805848</v>
+        <v>0.5213233169259976</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1688782302805848</v>
+        <v>0.1213233169259976</v>
       </c>
       <c r="D161" t="n">
-        <v>42.2195575701462</v>
+        <v>30.33082923149941</v>
       </c>
     </row>
     <row r="162">
@@ -2697,13 +2697,13 @@
         <v>0.06</v>
       </c>
       <c r="B162" t="n">
-        <v>0.06381495972907492</v>
+        <v>0.05721147332227933</v>
       </c>
       <c r="C162" t="n">
-        <v>0.003814959729074918</v>
+        <v>0.002788526677720671</v>
       </c>
       <c r="D162" t="n">
-        <v>6.358266215124864</v>
+        <v>4.647544462867785</v>
       </c>
     </row>
     <row r="163">
@@ -2711,13 +2711,13 @@
         <v>0.02</v>
       </c>
       <c r="B163" t="n">
-        <v>0.0387254253008662</v>
+        <v>0.02684254858907636</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0187254253008662</v>
+        <v>0.006842548589076364</v>
       </c>
       <c r="D163" t="n">
-        <v>93.627126504331</v>
+        <v>34.21274294538182</v>
       </c>
     </row>
     <row r="164">
@@ -2725,13 +2725,13 @@
         <v>0.88</v>
       </c>
       <c r="B164" t="n">
-        <v>0.6758624152944355</v>
+        <v>0.7740324985507447</v>
       </c>
       <c r="C164" t="n">
-        <v>0.2041375847055645</v>
+        <v>0.1059675014492553</v>
       </c>
       <c r="D164" t="n">
-        <v>23.19745280745052</v>
+        <v>12.04176152832446</v>
       </c>
     </row>
     <row r="165">
@@ -2739,13 +2739,13 @@
         <v>1</v>
       </c>
       <c r="B165" t="n">
-        <v>0.4296775143202844</v>
+        <v>0.4209579596418555</v>
       </c>
       <c r="C165" t="n">
-        <v>0.5703224856797156</v>
+        <v>0.5790420403581444</v>
       </c>
       <c r="D165" t="n">
-        <v>57.03224856797156</v>
+        <v>57.90420403581444</v>
       </c>
     </row>
     <row r="166">
@@ -2753,13 +2753,13 @@
         <v>0.3</v>
       </c>
       <c r="B166" t="n">
-        <v>0.2582244492916765</v>
+        <v>0.2346822797310007</v>
       </c>
       <c r="C166" t="n">
-        <v>0.04177555070832345</v>
+        <v>0.06531772026899926</v>
       </c>
       <c r="D166" t="n">
-        <v>13.92518356944115</v>
+        <v>21.77257342299976</v>
       </c>
     </row>
     <row r="167">
@@ -2767,13 +2767,13 @@
         <v>0.09</v>
       </c>
       <c r="B167" t="n">
-        <v>0.1767591095692779</v>
+        <v>0.1830790920150956</v>
       </c>
       <c r="C167" t="n">
-        <v>0.08675910956927788</v>
+        <v>0.09307909201509559</v>
       </c>
       <c r="D167" t="n">
-        <v>96.39901063253097</v>
+        <v>103.4212133501062</v>
       </c>
     </row>
     <row r="168">
@@ -2781,13 +2781,13 @@
         <v>0.24</v>
       </c>
       <c r="B168" t="n">
-        <v>0.3218654460278321</v>
+        <v>0.3047926666200292</v>
       </c>
       <c r="C168" t="n">
-        <v>0.08186544602783208</v>
+        <v>0.06479266662002925</v>
       </c>
       <c r="D168" t="n">
-        <v>34.1106025115967</v>
+        <v>26.99694442501219</v>
       </c>
     </row>
     <row r="169">
@@ -2795,13 +2795,13 @@
         <v>0.19</v>
       </c>
       <c r="B169" t="n">
-        <v>0.138362629288124</v>
+        <v>0.1400294493743338</v>
       </c>
       <c r="C169" t="n">
-        <v>0.05163737071187596</v>
+        <v>0.04997055062566619</v>
       </c>
       <c r="D169" t="n">
-        <v>27.1775635325663</v>
+        <v>26.3002898029822</v>
       </c>
     </row>
     <row r="170">
@@ -2809,13 +2809,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="B170" t="n">
-        <v>0.5300716921614185</v>
+        <v>0.5476887408831437</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1599283078385815</v>
+        <v>0.1423112591168563</v>
       </c>
       <c r="D170" t="n">
-        <v>23.17801562877992</v>
+        <v>20.62482016186323</v>
       </c>
     </row>
     <row r="171">
@@ -2823,13 +2823,13 @@
         <v>0.03</v>
       </c>
       <c r="B171" t="n">
-        <v>0.06324136771836819</v>
+        <v>0.05919308019292263</v>
       </c>
       <c r="C171" t="n">
-        <v>0.03324136771836819</v>
+        <v>0.02919308019292263</v>
       </c>
       <c r="D171" t="n">
-        <v>110.8045590612273</v>
+        <v>97.31026730974212</v>
       </c>
     </row>
     <row r="172">
@@ -2837,13 +2837,13 @@
         <v>0.3</v>
       </c>
       <c r="B172" t="n">
-        <v>0.3325509630491462</v>
+        <v>0.3209726764247587</v>
       </c>
       <c r="C172" t="n">
-        <v>0.03255096304914623</v>
+        <v>0.0209726764247587</v>
       </c>
       <c r="D172" t="n">
-        <v>10.85032101638208</v>
+        <v>6.990892141586233</v>
       </c>
     </row>
     <row r="173">
@@ -2851,13 +2851,13 @@
         <v>0.23</v>
       </c>
       <c r="B173" t="n">
-        <v>0.1782430587189773</v>
+        <v>0.1869490735134589</v>
       </c>
       <c r="C173" t="n">
-        <v>0.05175694128102273</v>
+        <v>0.04305092648654116</v>
       </c>
       <c r="D173" t="n">
-        <v>22.50301794827075</v>
+        <v>18.71779412458311</v>
       </c>
     </row>
     <row r="174">
@@ -2865,13 +2865,13 @@
         <v>0.01</v>
       </c>
       <c r="B174" t="n">
-        <v>0.04729890724953989</v>
+        <v>0.05756958887859021</v>
       </c>
       <c r="C174" t="n">
-        <v>0.03729890724953989</v>
+        <v>0.0475695888785902</v>
       </c>
       <c r="D174" t="n">
-        <v>372.9890724953988</v>
+        <v>475.695888785902</v>
       </c>
     </row>
     <row r="175">
@@ -2879,13 +2879,13 @@
         <v>0.09</v>
       </c>
       <c r="B175" t="n">
-        <v>0.1278493692141129</v>
+        <v>0.09279341777130429</v>
       </c>
       <c r="C175" t="n">
-        <v>0.03784936921411294</v>
+        <v>0.002793417771304291</v>
       </c>
       <c r="D175" t="n">
-        <v>42.05485468234772</v>
+        <v>3.103797523671434</v>
       </c>
     </row>
     <row r="176">
@@ -2893,13 +2893,13 @@
         <v>0.05</v>
       </c>
       <c r="B176" t="n">
-        <v>0.04981096217241954</v>
+        <v>0.01143363627834681</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0001890378275804655</v>
+        <v>0.03856636372165319</v>
       </c>
       <c r="D176" t="n">
-        <v>0.378075655160931</v>
+        <v>77.13272744330636</v>
       </c>
     </row>
     <row r="177">
@@ -2907,13 +2907,13 @@
         <v>0.5</v>
       </c>
       <c r="B177" t="n">
-        <v>0.3295617841474046</v>
+        <v>0.3225080740258339</v>
       </c>
       <c r="C177" t="n">
-        <v>0.1704382158525954</v>
+        <v>0.1774919259741661</v>
       </c>
       <c r="D177" t="n">
-        <v>34.08764317051908</v>
+        <v>35.49838519483323</v>
       </c>
     </row>
     <row r="178">
@@ -2921,13 +2921,13 @@
         <v>0.15</v>
       </c>
       <c r="B178" t="n">
-        <v>0.2070606892130523</v>
+        <v>0.3125859704040185</v>
       </c>
       <c r="C178" t="n">
-        <v>0.05706068921305232</v>
+        <v>0.1625859704040185</v>
       </c>
       <c r="D178" t="n">
-        <v>38.04045947536822</v>
+        <v>108.3906469360123</v>
       </c>
     </row>
     <row r="179">
@@ -2935,13 +2935,13 @@
         <v>0.01</v>
       </c>
       <c r="B179" t="n">
-        <v>0.1090786895789987</v>
+        <v>0.1220853720428084</v>
       </c>
       <c r="C179" t="n">
-        <v>0.09907868957899869</v>
+        <v>0.1120853720428084</v>
       </c>
       <c r="D179" t="n">
-        <v>990.7868957899868</v>
+        <v>1120.853720428084</v>
       </c>
     </row>
     <row r="180">
@@ -2949,13 +2949,13 @@
         <v>0.03</v>
       </c>
       <c r="B180" t="n">
-        <v>0.1453107454666817</v>
+        <v>0.04730833046157451</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1153107454666817</v>
+        <v>0.01730833046157451</v>
       </c>
       <c r="D180" t="n">
-        <v>384.3691515556055</v>
+        <v>57.69443487191504</v>
       </c>
     </row>
     <row r="181">
@@ -2963,13 +2963,13 @@
         <v>0.04</v>
       </c>
       <c r="B181" t="n">
-        <v>0.09107599523918453</v>
+        <v>0.08737396748068993</v>
       </c>
       <c r="C181" t="n">
-        <v>0.05107599523918453</v>
+        <v>0.04737396748068993</v>
       </c>
       <c r="D181" t="n">
-        <v>127.6899880979613</v>
+        <v>118.4349187017248</v>
       </c>
     </row>
     <row r="182">
@@ -2977,13 +2977,13 @@
         <v>0.03</v>
       </c>
       <c r="B182" t="n">
-        <v>0.03042134917073036</v>
+        <v>0.01777770973967907</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0004213491707303618</v>
+        <v>0.01222229026032093</v>
       </c>
       <c r="D182" t="n">
-        <v>1.404497235767873</v>
+        <v>40.7409675344031</v>
       </c>
     </row>
     <row r="183">
@@ -2991,13 +2991,13 @@
         <v>0.1</v>
       </c>
       <c r="B183" t="n">
-        <v>0.2492407958587478</v>
+        <v>0.2667663749771638</v>
       </c>
       <c r="C183" t="n">
-        <v>0.1492407958587477</v>
+        <v>0.1667663749771638</v>
       </c>
       <c r="D183" t="n">
-        <v>149.2407958587477</v>
+        <v>166.7663749771638</v>
       </c>
     </row>
     <row r="184">
@@ -3005,13 +3005,13 @@
         <v>0.14</v>
       </c>
       <c r="B184" t="n">
-        <v>0.05817551553389433</v>
+        <v>0.07690203620763369</v>
       </c>
       <c r="C184" t="n">
-        <v>0.08182448446610568</v>
+        <v>0.06309796379236632</v>
       </c>
       <c r="D184" t="n">
-        <v>58.44606033293262</v>
+        <v>45.06997413740451</v>
       </c>
     </row>
     <row r="185">
@@ -3019,13 +3019,13 @@
         <v>0.06</v>
       </c>
       <c r="B185" t="n">
-        <v>0.1003141766038205</v>
+        <v>0.1206628730479466</v>
       </c>
       <c r="C185" t="n">
-        <v>0.04031417660382047</v>
+        <v>0.0606628730479466</v>
       </c>
       <c r="D185" t="n">
-        <v>67.1902943397008</v>
+        <v>101.1047884132443</v>
       </c>
     </row>
     <row r="186">
@@ -3033,13 +3033,13 @@
         <v>0.17</v>
       </c>
       <c r="B186" t="n">
-        <v>0.0895861204429248</v>
+        <v>0.08963242462835697</v>
       </c>
       <c r="C186" t="n">
-        <v>0.08041387955707521</v>
+        <v>0.08036757537164305</v>
       </c>
       <c r="D186" t="n">
-        <v>47.30228209239718</v>
+        <v>47.27504433626061</v>
       </c>
     </row>
     <row r="187">
@@ -3047,13 +3047,13 @@
         <v>0.37</v>
       </c>
       <c r="B187" t="n">
-        <v>0.5817694830739996</v>
+        <v>0.5133739449804094</v>
       </c>
       <c r="C187" t="n">
-        <v>0.2117694830739996</v>
+        <v>0.1433739449804095</v>
       </c>
       <c r="D187" t="n">
-        <v>57.23499542540529</v>
+        <v>38.74971485957012</v>
       </c>
     </row>
     <row r="188">
@@ -3061,13 +3061,13 @@
         <v>0.04</v>
       </c>
       <c r="B188" t="n">
-        <v>0.08881037909019629</v>
+        <v>0.1093901192291408</v>
       </c>
       <c r="C188" t="n">
-        <v>0.04881037909019629</v>
+        <v>0.06939011922914076</v>
       </c>
       <c r="D188" t="n">
-        <v>122.0259477254907</v>
+        <v>173.4752980728519</v>
       </c>
     </row>
     <row r="189">
@@ -3075,13 +3075,13 @@
         <v>0.16</v>
       </c>
       <c r="B189" t="n">
-        <v>0.2455188345688499</v>
+        <v>0.2325273079454045</v>
       </c>
       <c r="C189" t="n">
-        <v>0.08551883456884993</v>
+        <v>0.07252730794540449</v>
       </c>
       <c r="D189" t="n">
-        <v>53.4492716055312</v>
+        <v>45.32956746587781</v>
       </c>
     </row>
     <row r="190">
@@ -3089,13 +3089,13 @@
         <v>0.11</v>
       </c>
       <c r="B190" t="n">
-        <v>0.08403092938619816</v>
+        <v>0.07950239506844131</v>
       </c>
       <c r="C190" t="n">
-        <v>0.02596907061380184</v>
+        <v>0.03049760493155869</v>
       </c>
       <c r="D190" t="n">
-        <v>23.60824601254713</v>
+        <v>27.72509539232608</v>
       </c>
     </row>
     <row r="191">
@@ -3103,13 +3103,13 @@
         <v>0.12</v>
       </c>
       <c r="B191" t="n">
-        <v>0.157560964494479</v>
+        <v>0.1557390818567185</v>
       </c>
       <c r="C191" t="n">
-        <v>0.03756096449447904</v>
+        <v>0.03573908185671854</v>
       </c>
       <c r="D191" t="n">
-        <v>31.3008037453992</v>
+        <v>29.78256821393212</v>
       </c>
     </row>
     <row r="192">
@@ -3117,13 +3117,13 @@
         <v>0.6</v>
       </c>
       <c r="B192" t="n">
-        <v>0.4420291464052851</v>
+        <v>0.3698392991929869</v>
       </c>
       <c r="C192" t="n">
-        <v>0.1579708535947149</v>
+        <v>0.2301607008070131</v>
       </c>
       <c r="D192" t="n">
-        <v>26.32847559911914</v>
+        <v>38.36011680116885</v>
       </c>
     </row>
     <row r="193">
@@ -3131,13 +3131,13 @@
         <v>0.19</v>
       </c>
       <c r="B193" t="n">
-        <v>0.1497124922439308</v>
+        <v>0.1582459891637451</v>
       </c>
       <c r="C193" t="n">
-        <v>0.04028750775606921</v>
+        <v>0.0317540108362549</v>
       </c>
       <c r="D193" t="n">
-        <v>21.20395145056274</v>
+        <v>16.71263728223942</v>
       </c>
     </row>
     <row r="194">
@@ -3145,13 +3145,13 @@
         <v>0.05</v>
       </c>
       <c r="B194" t="n">
-        <v>0.04773842779902782</v>
+        <v>0.0559906238863595</v>
       </c>
       <c r="C194" t="n">
-        <v>0.002261572200972187</v>
+        <v>0.0059906238863595</v>
       </c>
       <c r="D194" t="n">
-        <v>4.523144401944373</v>
+        <v>11.981247772719</v>
       </c>
     </row>
     <row r="195">
@@ -3159,13 +3159,13 @@
         <v>0.06</v>
       </c>
       <c r="B195" t="n">
-        <v>0.1311133379514527</v>
+        <v>0.1370098604582935</v>
       </c>
       <c r="C195" t="n">
-        <v>0.07111333795145275</v>
+        <v>0.0770098604582935</v>
       </c>
       <c r="D195" t="n">
-        <v>118.5222299190879</v>
+        <v>128.3497674304892</v>
       </c>
     </row>
     <row r="196">
@@ -3173,13 +3173,13 @@
         <v>0.03</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0642667016578391</v>
+        <v>0.04391392707767472</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0342667016578391</v>
+        <v>0.01391392707767472</v>
       </c>
       <c r="D196" t="n">
-        <v>114.2223388594637</v>
+        <v>46.37975692558241</v>
       </c>
     </row>
     <row r="197">
@@ -3187,13 +3187,13 @@
         <v>0.05</v>
       </c>
       <c r="B197" t="n">
-        <v>0.1891205843194471</v>
+        <v>0.1881722459009646</v>
       </c>
       <c r="C197" t="n">
-        <v>0.1391205843194471</v>
+        <v>0.1381722459009646</v>
       </c>
       <c r="D197" t="n">
-        <v>278.2411686388942</v>
+        <v>276.3444918019292</v>
       </c>
     </row>
     <row r="198">
@@ -3201,13 +3201,13 @@
         <v>0.04</v>
       </c>
       <c r="B198" t="n">
-        <v>0.06057543041633295</v>
+        <v>0.04095894479372469</v>
       </c>
       <c r="C198" t="n">
-        <v>0.02057543041633295</v>
+        <v>0.0009589447937246934</v>
       </c>
       <c r="D198" t="n">
-        <v>51.43857604083239</v>
+        <v>2.397361984311734</v>
       </c>
     </row>
     <row r="199">
@@ -3215,13 +3215,13 @@
         <v>0.04</v>
       </c>
       <c r="B199" t="n">
-        <v>0.04532912351315721</v>
+        <v>0.01068973532324491</v>
       </c>
       <c r="C199" t="n">
-        <v>0.005329123513157209</v>
+        <v>0.02931026467675509</v>
       </c>
       <c r="D199" t="n">
-        <v>13.32280878289302</v>
+        <v>73.27566169188773</v>
       </c>
     </row>
     <row r="200">
@@ -3229,13 +3229,13 @@
         <v>0.02</v>
       </c>
       <c r="B200" t="n">
-        <v>0.04847523076284765</v>
+        <v>0.04698181436146187</v>
       </c>
       <c r="C200" t="n">
-        <v>0.02847523076284765</v>
+        <v>0.02698181436146187</v>
       </c>
       <c r="D200" t="n">
-        <v>142.3761538142383</v>
+        <v>134.9090718073093</v>
       </c>
     </row>
     <row r="201">
@@ -3243,13 +3243,13 @@
         <v>0.2</v>
       </c>
       <c r="B201" t="n">
-        <v>0.3859679694264348</v>
+        <v>0.3699846038521285</v>
       </c>
       <c r="C201" t="n">
-        <v>0.1859679694264348</v>
+        <v>0.1699846038521285</v>
       </c>
       <c r="D201" t="n">
-        <v>92.9839847132174</v>
+        <v>84.99230192606424</v>
       </c>
     </row>
     <row r="202">
@@ -3257,13 +3257,13 @@
         <v>0.22</v>
       </c>
       <c r="B202" t="n">
-        <v>0.2599163799034929</v>
+        <v>0.2107826730473872</v>
       </c>
       <c r="C202" t="n">
-        <v>0.03991637990349292</v>
+        <v>0.009217326952612764</v>
       </c>
       <c r="D202" t="n">
-        <v>18.14380904704224</v>
+        <v>4.189694069369438</v>
       </c>
     </row>
     <row r="203">
@@ -3271,13 +3271,13 @@
         <v>0.29</v>
       </c>
       <c r="B203" t="n">
-        <v>0.3537472017096007</v>
+        <v>0.3254323365811158</v>
       </c>
       <c r="C203" t="n">
-        <v>0.06374720170960069</v>
+        <v>0.03543233658111583</v>
       </c>
       <c r="D203" t="n">
-        <v>21.98179369296576</v>
+        <v>12.21804709693649</v>
       </c>
     </row>
     <row r="204">
@@ -3285,13 +3285,13 @@
         <v>0.48</v>
       </c>
       <c r="B204" t="n">
-        <v>0.5116514596211303</v>
+        <v>0.4601278891669857</v>
       </c>
       <c r="C204" t="n">
-        <v>0.03165145962113036</v>
+        <v>0.01987211083301427</v>
       </c>
       <c r="D204" t="n">
-        <v>6.594054087735493</v>
+        <v>4.140023090211306</v>
       </c>
     </row>
     <row r="205">
@@ -3299,13 +3299,13 @@
         <v>0.13</v>
       </c>
       <c r="B205" t="n">
-        <v>0.1974360615347011</v>
+        <v>0.1935617709561096</v>
       </c>
       <c r="C205" t="n">
-        <v>0.06743606153470105</v>
+        <v>0.0635617709561096</v>
       </c>
       <c r="D205" t="n">
-        <v>51.87389348823158</v>
+        <v>48.89366996623815</v>
       </c>
     </row>
     <row r="206">
@@ -3313,13 +3313,13 @@
         <v>0.63</v>
       </c>
       <c r="B206" t="n">
-        <v>0.2616223945151938</v>
+        <v>0.2478203806016778</v>
       </c>
       <c r="C206" t="n">
-        <v>0.3683776054848062</v>
+        <v>0.3821796193983222</v>
       </c>
       <c r="D206" t="n">
-        <v>58.47263579123908</v>
+        <v>60.66343165052734</v>
       </c>
     </row>
     <row r="207">
@@ -3327,13 +3327,13 @@
         <v>0.03</v>
       </c>
       <c r="B207" t="n">
-        <v>0.05395764880751597</v>
+        <v>0.04514662457260904</v>
       </c>
       <c r="C207" t="n">
-        <v>0.02395764880751597</v>
+        <v>0.01514662457260904</v>
       </c>
       <c r="D207" t="n">
-        <v>79.85882935838656</v>
+        <v>50.48874857536347</v>
       </c>
     </row>
     <row r="208">
@@ -3341,13 +3341,13 @@
         <v>0.57</v>
       </c>
       <c r="B208" t="n">
-        <v>0.4257754577314207</v>
+        <v>0.4079853349380522</v>
       </c>
       <c r="C208" t="n">
-        <v>0.1442245422685793</v>
+        <v>0.1620146650619478</v>
       </c>
       <c r="D208" t="n">
-        <v>25.30255127518935</v>
+        <v>28.42362544946452</v>
       </c>
     </row>
     <row r="209">
@@ -3355,13 +3355,13 @@
         <v>0.06</v>
       </c>
       <c r="B209" t="n">
-        <v>0.07338127069073108</v>
+        <v>0.0878182545367337</v>
       </c>
       <c r="C209" t="n">
-        <v>0.01338127069073108</v>
+        <v>0.0278182545367337</v>
       </c>
       <c r="D209" t="n">
-        <v>22.30211781788514</v>
+        <v>46.36375756122283</v>
       </c>
     </row>
     <row r="210">
@@ -3369,13 +3369,13 @@
         <v>0.06</v>
       </c>
       <c r="B210" t="n">
-        <v>0.06844347064999101</v>
+        <v>0.05681030099847717</v>
       </c>
       <c r="C210" t="n">
-        <v>0.008443470649991014</v>
+        <v>0.003189699001522828</v>
       </c>
       <c r="D210" t="n">
-        <v>14.07245108331836</v>
+        <v>5.316165002538047</v>
       </c>
     </row>
     <row r="211">
@@ -3383,13 +3383,13 @@
         <v>0.09</v>
       </c>
       <c r="B211" t="n">
-        <v>0.2553696332149404</v>
+        <v>0.2551392919307802</v>
       </c>
       <c r="C211" t="n">
-        <v>0.1653696332149404</v>
+        <v>0.1651392919307802</v>
       </c>
       <c r="D211" t="n">
-        <v>183.7440369054893</v>
+        <v>183.4881021453114</v>
       </c>
     </row>
     <row r="212">
@@ -3397,13 +3397,13 @@
         <v>0.36</v>
       </c>
       <c r="B212" t="n">
-        <v>0.4548166945235284</v>
+        <v>0.4027021426969464</v>
       </c>
       <c r="C212" t="n">
-        <v>0.09481669452352837</v>
+        <v>0.04270214269694639</v>
       </c>
       <c r="D212" t="n">
-        <v>26.3379707009801</v>
+        <v>11.86170630470733</v>
       </c>
     </row>
     <row r="213">
@@ -3411,13 +3411,13 @@
         <v>0.11</v>
       </c>
       <c r="B213" t="n">
-        <v>0.05756223588862297</v>
+        <v>0.0506136764071321</v>
       </c>
       <c r="C213" t="n">
-        <v>0.05243776411137703</v>
+        <v>0.0593863235928679</v>
       </c>
       <c r="D213" t="n">
-        <v>47.67069464670639</v>
+        <v>53.98756690260718</v>
       </c>
     </row>
     <row r="214">
@@ -3425,13 +3425,13 @@
         <v>0.08</v>
       </c>
       <c r="B214" t="n">
-        <v>0.1486531346677737</v>
+        <v>0.1371111078106375</v>
       </c>
       <c r="C214" t="n">
-        <v>0.06865313466777374</v>
+        <v>0.05711110781063745</v>
       </c>
       <c r="D214" t="n">
-        <v>85.81641833471718</v>
+        <v>71.38888476329682</v>
       </c>
     </row>
     <row r="215">
@@ -3439,13 +3439,13 @@
         <v>0.05</v>
       </c>
       <c r="B215" t="n">
-        <v>0.07347030651566788</v>
+        <v>0.06844860122388247</v>
       </c>
       <c r="C215" t="n">
-        <v>0.02347030651566788</v>
+        <v>0.01844860122388246</v>
       </c>
       <c r="D215" t="n">
-        <v>46.94061303133576</v>
+        <v>36.89720244776493</v>
       </c>
     </row>
     <row r="216">
@@ -3453,13 +3453,13 @@
         <v>0.22</v>
       </c>
       <c r="B216" t="n">
-        <v>0.4274859390915846</v>
+        <v>0.4535142210246669</v>
       </c>
       <c r="C216" t="n">
-        <v>0.2074859390915846</v>
+        <v>0.2335142210246669</v>
       </c>
       <c r="D216" t="n">
-        <v>94.31179049617482</v>
+        <v>106.142827738485</v>
       </c>
     </row>
     <row r="217">
@@ -3467,13 +3467,13 @@
         <v>0.09</v>
       </c>
       <c r="B217" t="n">
-        <v>0.07445620374283202</v>
+        <v>0.07717488954381768</v>
       </c>
       <c r="C217" t="n">
-        <v>0.01554379625716798</v>
+        <v>0.01282511045618231</v>
       </c>
       <c r="D217" t="n">
-        <v>17.27088473018664</v>
+        <v>14.25012272909146</v>
       </c>
     </row>
     <row r="218">
@@ -3481,13 +3481,13 @@
         <v>0.01</v>
       </c>
       <c r="B218" t="n">
-        <v>0.07986338015043093</v>
+        <v>0.08258514353104851</v>
       </c>
       <c r="C218" t="n">
-        <v>0.06986338015043093</v>
+        <v>0.07258514353104852</v>
       </c>
       <c r="D218" t="n">
-        <v>698.6338015043093</v>
+        <v>725.8514353104852</v>
       </c>
     </row>
     <row r="219">
@@ -3495,13 +3495,13 @@
         <v>1</v>
       </c>
       <c r="B219" t="n">
-        <v>0.430736011841435</v>
+        <v>0.4643615460915931</v>
       </c>
       <c r="C219" t="n">
-        <v>0.569263988158565</v>
+        <v>0.5356384539084069</v>
       </c>
       <c r="D219" t="n">
-        <v>56.9263988158565</v>
+        <v>53.56384539084069</v>
       </c>
     </row>
     <row r="220">
@@ -3509,13 +3509,13 @@
         <v>0.05</v>
       </c>
       <c r="B220" t="n">
-        <v>0.04800983298338191</v>
+        <v>0.01949669708351898</v>
       </c>
       <c r="C220" t="n">
-        <v>0.001990167016618097</v>
+        <v>0.03050330291648103</v>
       </c>
       <c r="D220" t="n">
-        <v>3.980334033236193</v>
+        <v>61.00660583296204</v>
       </c>
     </row>
     <row r="221">
@@ -3523,13 +3523,13 @@
         <v>0.02</v>
       </c>
       <c r="B221" t="n">
-        <v>0.04667075413771604</v>
+        <v>0.05867747958943392</v>
       </c>
       <c r="C221" t="n">
-        <v>0.02667075413771604</v>
+        <v>0.03867747958943392</v>
       </c>
       <c r="D221" t="n">
-        <v>133.3537706885802</v>
+        <v>193.3873979471696</v>
       </c>
     </row>
     <row r="222">
@@ -3537,13 +3537,13 @@
         <v>0.17</v>
       </c>
       <c r="B222" t="n">
-        <v>0.1529551575632712</v>
+        <v>0.1683957026175374</v>
       </c>
       <c r="C222" t="n">
-        <v>0.0170448424367288</v>
+        <v>0.001604297382462622</v>
       </c>
       <c r="D222" t="n">
-        <v>10.02637790395812</v>
+        <v>0.9437043426250714</v>
       </c>
     </row>
     <row r="223">
@@ -3551,13 +3551,13 @@
         <v>0.16</v>
       </c>
       <c r="B223" t="n">
-        <v>0.2678005222956468</v>
+        <v>0.2739954593894092</v>
       </c>
       <c r="C223" t="n">
-        <v>0.1078005222956468</v>
+        <v>0.1139954593894092</v>
       </c>
       <c r="D223" t="n">
-        <v>67.37532643477923</v>
+        <v>71.24716211838073</v>
       </c>
     </row>
     <row r="224">
@@ -3565,13 +3565,13 @@
         <v>0.39</v>
       </c>
       <c r="B224" t="n">
-        <v>0.3493844582418569</v>
+        <v>0.3323860663502787</v>
       </c>
       <c r="C224" t="n">
-        <v>0.04061554175814314</v>
+        <v>0.05761393364972134</v>
       </c>
       <c r="D224" t="n">
-        <v>10.41424147644696</v>
+        <v>14.77280349992855</v>
       </c>
     </row>
     <row r="225">
@@ -3579,13 +3579,13 @@
         <v>0.24</v>
       </c>
       <c r="B225" t="n">
-        <v>0.3260315441112535</v>
+        <v>0.3010004962125457</v>
       </c>
       <c r="C225" t="n">
-        <v>0.08603154411125352</v>
+        <v>0.06100049621254566</v>
       </c>
       <c r="D225" t="n">
-        <v>35.8464767130223</v>
+        <v>25.41687342189402</v>
       </c>
     </row>
     <row r="226">
@@ -3593,13 +3593,13 @@
         <v>0.09</v>
       </c>
       <c r="B226" t="n">
-        <v>0.2366143280955701</v>
+        <v>0.2272785299532168</v>
       </c>
       <c r="C226" t="n">
-        <v>0.1466143280955701</v>
+        <v>0.1372785299532168</v>
       </c>
       <c r="D226" t="n">
-        <v>162.9048089950779</v>
+        <v>152.5316999480187</v>
       </c>
     </row>
     <row r="227">
@@ -3607,13 +3607,13 @@
         <v>0.04</v>
       </c>
       <c r="B227" t="n">
-        <v>0.07786257398275542</v>
+        <v>0.02404985415841282</v>
       </c>
       <c r="C227" t="n">
-        <v>0.03786257398275542</v>
+        <v>0.01595014584158718</v>
       </c>
       <c r="D227" t="n">
-        <v>94.65643495688856</v>
+        <v>39.87536460396795</v>
       </c>
     </row>
     <row r="228">
@@ -3621,13 +3621,13 @@
         <v>0.04</v>
       </c>
       <c r="B228" t="n">
-        <v>0.07579259166909713</v>
+        <v>0.07564678830430899</v>
       </c>
       <c r="C228" t="n">
-        <v>0.03579259166909713</v>
+        <v>0.03564678830430899</v>
       </c>
       <c r="D228" t="n">
-        <v>89.48147917274282</v>
+        <v>89.11697076077246</v>
       </c>
     </row>
     <row r="229">
@@ -3635,13 +3635,13 @@
         <v>0.18</v>
       </c>
       <c r="B229" t="n">
-        <v>0.08729109425031434</v>
+        <v>0.09122631275605619</v>
       </c>
       <c r="C229" t="n">
-        <v>0.09270890574968566</v>
+        <v>0.0887736872439438</v>
       </c>
       <c r="D229" t="n">
-        <v>51.50494763871426</v>
+        <v>49.31871513552434</v>
       </c>
     </row>
     <row r="230">
@@ -3649,13 +3649,13 @@
         <v>0.03</v>
       </c>
       <c r="B230" t="n">
-        <v>0.09784396877235124</v>
+        <v>0.08338703423886745</v>
       </c>
       <c r="C230" t="n">
-        <v>0.06784396877235124</v>
+        <v>0.05338703423886745</v>
       </c>
       <c r="D230" t="n">
-        <v>226.1465625745041</v>
+        <v>177.9567807962248</v>
       </c>
     </row>
     <row r="231">
@@ -3663,13 +3663,13 @@
         <v>0.33</v>
       </c>
       <c r="B231" t="n">
-        <v>0.2757657654704339</v>
+        <v>0.3033033884060552</v>
       </c>
       <c r="C231" t="n">
-        <v>0.05423423452956616</v>
+        <v>0.02669661159394482</v>
       </c>
       <c r="D231" t="n">
-        <v>16.43461652411096</v>
+        <v>8.089882301195399</v>
       </c>
     </row>
     <row r="232">
@@ -3677,13 +3677,13 @@
         <v>0.11</v>
       </c>
       <c r="B232" t="n">
-        <v>0.1050744258474696</v>
+        <v>0.1307065673275556</v>
       </c>
       <c r="C232" t="n">
-        <v>0.004925574152530379</v>
+        <v>0.02070656732755564</v>
       </c>
       <c r="D232" t="n">
-        <v>4.477794684118527</v>
+        <v>18.82415211595968</v>
       </c>
     </row>
     <row r="233">
@@ -3691,13 +3691,13 @@
         <v>0.11</v>
       </c>
       <c r="B233" t="n">
-        <v>0.1194574895913626</v>
+        <v>0.1095279454959139</v>
       </c>
       <c r="C233" t="n">
-        <v>0.009457489591362597</v>
+        <v>0.0004720545040861196</v>
       </c>
       <c r="D233" t="n">
-        <v>8.597717810329634</v>
+        <v>0.4291404582601088</v>
       </c>
     </row>
     <row r="234">
@@ -3705,13 +3705,13 @@
         <v>0.03</v>
       </c>
       <c r="B234" t="n">
-        <v>0.07186389266669935</v>
+        <v>0.06360656581922491</v>
       </c>
       <c r="C234" t="n">
-        <v>0.04186389266669935</v>
+        <v>0.03360656581922492</v>
       </c>
       <c r="D234" t="n">
-        <v>139.5463088889978</v>
+        <v>112.021886064083</v>
       </c>
     </row>
     <row r="235">
@@ -3719,13 +3719,13 @@
         <v>0.22</v>
       </c>
       <c r="B235" t="n">
-        <v>0.1203713815061351</v>
+        <v>0.150249264996146</v>
       </c>
       <c r="C235" t="n">
-        <v>0.09962861849386487</v>
+        <v>0.06975073500385401</v>
       </c>
       <c r="D235" t="n">
-        <v>45.28573567902949</v>
+        <v>31.70487954720637</v>
       </c>
     </row>
     <row r="236">
@@ -3733,13 +3733,13 @@
         <v>0.2</v>
       </c>
       <c r="B236" t="n">
-        <v>0.08154117520152593</v>
+        <v>0.094014718714723</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1184588247984741</v>
+        <v>0.105985281285277</v>
       </c>
       <c r="D236" t="n">
-        <v>59.22941239923703</v>
+        <v>52.9926406426385</v>
       </c>
     </row>
     <row r="237">
@@ -3747,13 +3747,13 @@
         <v>0.01</v>
       </c>
       <c r="B237" t="n">
-        <v>0.1025484426194313</v>
+        <v>0.1058279735568888</v>
       </c>
       <c r="C237" t="n">
-        <v>0.09254844261943131</v>
+        <v>0.09582797355688884</v>
       </c>
       <c r="D237" t="n">
-        <v>925.4844261943131</v>
+        <v>958.2797355688884</v>
       </c>
     </row>
     <row r="238">
@@ -3761,13 +3761,13 @@
         <v>0.08</v>
       </c>
       <c r="B238" t="n">
-        <v>0.04941008382023837</v>
+        <v>0.02794160521609101</v>
       </c>
       <c r="C238" t="n">
-        <v>0.03058991617976163</v>
+        <v>0.05205839478390899</v>
       </c>
       <c r="D238" t="n">
-        <v>38.23739522470203</v>
+        <v>65.07299347988624</v>
       </c>
     </row>
     <row r="239">
@@ -3775,13 +3775,13 @@
         <v>0.03</v>
       </c>
       <c r="B239" t="n">
-        <v>0.0484837769750619</v>
+        <v>0.07414676441528151</v>
       </c>
       <c r="C239" t="n">
-        <v>0.0184837769750619</v>
+        <v>0.04414676441528151</v>
       </c>
       <c r="D239" t="n">
-        <v>61.61258991687301</v>
+        <v>147.1558813842717</v>
       </c>
     </row>
     <row r="240">
@@ -3789,13 +3789,13 @@
         <v>0.08</v>
       </c>
       <c r="B240" t="n">
-        <v>0.09658320286165067</v>
+        <v>0.1146154491728986</v>
       </c>
       <c r="C240" t="n">
-        <v>0.01658320286165067</v>
+        <v>0.03461544917289856</v>
       </c>
       <c r="D240" t="n">
-        <v>20.72900357706334</v>
+        <v>43.2693114661232</v>
       </c>
     </row>
     <row r="241">
@@ -3803,13 +3803,13 @@
         <v>0.11</v>
       </c>
       <c r="B241" t="n">
-        <v>0.1249730643332435</v>
+        <v>0.0986533550757957</v>
       </c>
       <c r="C241" t="n">
-        <v>0.01497306433324345</v>
+        <v>0.0113466449242043</v>
       </c>
       <c r="D241" t="n">
-        <v>13.61187666658496</v>
+        <v>10.31513174927664</v>
       </c>
     </row>
     <row r="242">
@@ -3817,13 +3817,13 @@
         <v>0.04</v>
       </c>
       <c r="B242" t="n">
-        <v>0.1252914766767062</v>
+        <v>0.03708252468163892</v>
       </c>
       <c r="C242" t="n">
-        <v>0.0852914766767062</v>
+        <v>0.002917475318361083</v>
       </c>
       <c r="D242" t="n">
-        <v>213.2286916917655</v>
+        <v>7.293688295902707</v>
       </c>
     </row>
     <row r="243">
@@ -3831,13 +3831,13 @@
         <v>0.13</v>
       </c>
       <c r="B243" t="n">
-        <v>0.1151341859255377</v>
+        <v>0.09770421009480035</v>
       </c>
       <c r="C243" t="n">
-        <v>0.0148658140744623</v>
+        <v>0.03229578990519966</v>
       </c>
       <c r="D243" t="n">
-        <v>11.43524159574023</v>
+        <v>24.84291531169204</v>
       </c>
     </row>
     <row r="244">
@@ -3845,13 +3845,13 @@
         <v>0.79</v>
       </c>
       <c r="B244" t="n">
-        <v>0.2610944603532331</v>
+        <v>0.2897346051326554</v>
       </c>
       <c r="C244" t="n">
-        <v>0.528905539646767</v>
+        <v>0.5002653948673447</v>
       </c>
       <c r="D244" t="n">
-        <v>66.95006830971734</v>
+        <v>63.32473352751198</v>
       </c>
     </row>
     <row r="245">
@@ -3859,13 +3859,13 @@
         <v>0.29</v>
       </c>
       <c r="B245" t="n">
-        <v>0.1995699818231075</v>
+        <v>0.2188772683107053</v>
       </c>
       <c r="C245" t="n">
-        <v>0.0904300181768925</v>
+        <v>0.07112273168929473</v>
       </c>
       <c r="D245" t="n">
-        <v>31.18276488858363</v>
+        <v>24.52507989286025</v>
       </c>
     </row>
     <row r="246">
@@ -3873,13 +3873,13 @@
         <v>0.37</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1707196367114879</v>
+        <v>0.1517420445017549</v>
       </c>
       <c r="C246" t="n">
-        <v>0.1992803632885121</v>
+        <v>0.2182579554982451</v>
       </c>
       <c r="D246" t="n">
-        <v>53.8595576455438</v>
+        <v>58.98863662114733</v>
       </c>
     </row>
     <row r="247">
@@ -3887,13 +3887,13 @@
         <v>0.02</v>
       </c>
       <c r="B247" t="n">
-        <v>0.03152288462164787</v>
+        <v>0.0215168079264117</v>
       </c>
       <c r="C247" t="n">
-        <v>0.01152288462164787</v>
+        <v>0.001516807926411696</v>
       </c>
       <c r="D247" t="n">
-        <v>57.61442310823936</v>
+        <v>7.584039632058478</v>
       </c>
     </row>
     <row r="248">
@@ -3901,13 +3901,13 @@
         <v>0.32</v>
       </c>
       <c r="B248" t="n">
-        <v>0.07255120572843332</v>
+        <v>0.05663188746979952</v>
       </c>
       <c r="C248" t="n">
-        <v>0.2474487942715667</v>
+        <v>0.2633681125302005</v>
       </c>
       <c r="D248" t="n">
-        <v>77.32774820986459</v>
+        <v>82.30253516568766</v>
       </c>
     </row>
     <row r="249">
@@ -3915,13 +3915,13 @@
         <v>0.1</v>
       </c>
       <c r="B249" t="n">
-        <v>0.2156034987104483</v>
+        <v>0.1819800032468272</v>
       </c>
       <c r="C249" t="n">
-        <v>0.1156034987104483</v>
+        <v>0.08198000324682722</v>
       </c>
       <c r="D249" t="n">
-        <v>115.6034987104483</v>
+        <v>81.98000324682721</v>
       </c>
     </row>
     <row r="250">
@@ -3929,13 +3929,13 @@
         <v>0.06</v>
       </c>
       <c r="B250" t="n">
-        <v>0.08178595822697055</v>
+        <v>0.09498022172192938</v>
       </c>
       <c r="C250" t="n">
-        <v>0.02178595822697055</v>
+        <v>0.03498022172192938</v>
       </c>
       <c r="D250" t="n">
-        <v>36.30993037828425</v>
+        <v>58.30036953654898</v>
       </c>
     </row>
     <row r="251">
@@ -3943,13 +3943,13 @@
         <v>0.17</v>
       </c>
       <c r="B251" t="n">
-        <v>0.2391611898483704</v>
+        <v>0.2381233811069893</v>
       </c>
       <c r="C251" t="n">
-        <v>0.06916118984837041</v>
+        <v>0.06812338110698932</v>
       </c>
       <c r="D251" t="n">
-        <v>40.68305285198259</v>
+        <v>40.07257712175842</v>
       </c>
     </row>
     <row r="252">
@@ -3957,13 +3957,13 @@
         <v>0.1</v>
       </c>
       <c r="B252" t="n">
-        <v>0.07874881045299442</v>
+        <v>0.04547166360679955</v>
       </c>
       <c r="C252" t="n">
-        <v>0.02125118954700558</v>
+        <v>0.05452833639320046</v>
       </c>
       <c r="D252" t="n">
-        <v>21.25118954700558</v>
+        <v>54.52833639320045</v>
       </c>
     </row>
     <row r="253">
@@ -3971,13 +3971,13 @@
         <v>0.22</v>
       </c>
       <c r="B253" t="n">
-        <v>0.3116064657929924</v>
+        <v>0.3023047689661127</v>
       </c>
       <c r="C253" t="n">
-        <v>0.09160646579299245</v>
+        <v>0.08230476896611275</v>
       </c>
       <c r="D253" t="n">
-        <v>41.63930263317839</v>
+        <v>37.41125862096034</v>
       </c>
     </row>
     <row r="254">
@@ -3985,13 +3985,13 @@
         <v>0.33</v>
       </c>
       <c r="B254" t="n">
-        <v>0.4238462205097666</v>
+        <v>0.3317942228980511</v>
       </c>
       <c r="C254" t="n">
-        <v>0.0938462205097666</v>
+        <v>0.00179422289805109</v>
       </c>
       <c r="D254" t="n">
-        <v>28.43824863932321</v>
+        <v>0.5437039085003302</v>
       </c>
     </row>
     <row r="255">
@@ -3999,13 +3999,13 @@
         <v>0.06</v>
       </c>
       <c r="B255" t="n">
-        <v>0.08696516981177449</v>
+        <v>0.07158861402761563</v>
       </c>
       <c r="C255" t="n">
-        <v>0.02696516981177449</v>
+        <v>0.01158861402761563</v>
       </c>
       <c r="D255" t="n">
-        <v>44.94194968629082</v>
+        <v>19.31435671269271</v>
       </c>
     </row>
     <row r="256">
@@ -4013,13 +4013,13 @@
         <v>0.2</v>
       </c>
       <c r="B256" t="n">
-        <v>0.3234306716022137</v>
+        <v>0.3455127610892977</v>
       </c>
       <c r="C256" t="n">
-        <v>0.1234306716022137</v>
+        <v>0.1455127610892977</v>
       </c>
       <c r="D256" t="n">
-        <v>61.71533580110685</v>
+        <v>72.75638054464886</v>
       </c>
     </row>
     <row r="257">
@@ -4027,13 +4027,13 @@
         <v>0.08</v>
       </c>
       <c r="B257" t="n">
-        <v>0.08701826869861162</v>
+        <v>0.1030767557866091</v>
       </c>
       <c r="C257" t="n">
-        <v>0.007018268698611621</v>
+        <v>0.02307675578660913</v>
       </c>
       <c r="D257" t="n">
-        <v>8.772835873264526</v>
+        <v>28.84594473326142</v>
       </c>
     </row>
     <row r="258">
@@ -4041,13 +4041,13 @@
         <v>0.12</v>
       </c>
       <c r="B258" t="n">
-        <v>0.173056631980828</v>
+        <v>0.1647802776668085</v>
       </c>
       <c r="C258" t="n">
-        <v>0.053056631980828</v>
+        <v>0.04478027766680853</v>
       </c>
       <c r="D258" t="n">
-        <v>44.21385998402333</v>
+        <v>37.31689805567378</v>
       </c>
     </row>
     <row r="259">
@@ -4055,13 +4055,13 @@
         <v>0.38</v>
       </c>
       <c r="B259" t="n">
-        <v>0.2709106144535014</v>
+        <v>0.2585595347387713</v>
       </c>
       <c r="C259" t="n">
-        <v>0.1090893855464986</v>
+        <v>0.1214404652612287</v>
       </c>
       <c r="D259" t="n">
-        <v>28.70773303855226</v>
+        <v>31.95801717400755</v>
       </c>
     </row>
     <row r="260">
@@ -4069,13 +4069,13 @@
         <v>0.7</v>
       </c>
       <c r="B260" t="n">
-        <v>0.6165521292758749</v>
+        <v>0.4677154124643096</v>
       </c>
       <c r="C260" t="n">
-        <v>0.08344787072412507</v>
+        <v>0.2322845875356903</v>
       </c>
       <c r="D260" t="n">
-        <v>11.92112438916073</v>
+        <v>33.18351250509862</v>
       </c>
     </row>
     <row r="261">
@@ -4083,13 +4083,13 @@
         <v>0.22</v>
       </c>
       <c r="B261" t="n">
-        <v>0.05802913239769758</v>
+        <v>0.02084229770714441</v>
       </c>
       <c r="C261" t="n">
-        <v>0.1619708676023024</v>
+        <v>0.1991577022928556</v>
       </c>
       <c r="D261" t="n">
-        <v>73.62312163741019</v>
+        <v>90.52622831493437</v>
       </c>
     </row>
     <row r="262">
@@ -4097,13 +4097,13 @@
         <v>0.15</v>
       </c>
       <c r="B262" t="n">
-        <v>0.185409673531518</v>
+        <v>0.2051972422560206</v>
       </c>
       <c r="C262" t="n">
-        <v>0.03540967353151805</v>
+        <v>0.0551972422560206</v>
       </c>
       <c r="D262" t="n">
-        <v>23.60644902101204</v>
+        <v>36.79816150401373</v>
       </c>
     </row>
     <row r="263">
@@ -4111,13 +4111,13 @@
         <v>0.15</v>
       </c>
       <c r="B263" t="n">
-        <v>0.3236899131358094</v>
+        <v>0.2952399245136977</v>
       </c>
       <c r="C263" t="n">
-        <v>0.1736899131358094</v>
+        <v>0.1452399245136977</v>
       </c>
       <c r="D263" t="n">
-        <v>115.7932754238729</v>
+        <v>96.82661634246513</v>
       </c>
     </row>
     <row r="264">
@@ -4125,13 +4125,13 @@
         <v>0.16</v>
       </c>
       <c r="B264" t="n">
-        <v>0.2204039633777989</v>
+        <v>0.2106555366434653</v>
       </c>
       <c r="C264" t="n">
-        <v>0.06040396337779894</v>
+        <v>0.05065553664346531</v>
       </c>
       <c r="D264" t="n">
-        <v>37.75247711112434</v>
+        <v>31.65971040216582</v>
       </c>
     </row>
     <row r="265">
@@ -4139,13 +4139,13 @@
         <v>0.51</v>
       </c>
       <c r="B265" t="n">
-        <v>0.5059535316150626</v>
+        <v>0.5035751896908626</v>
       </c>
       <c r="C265" t="n">
-        <v>0.004046468384937385</v>
+        <v>0.006424810309137441</v>
       </c>
       <c r="D265" t="n">
-        <v>0.7934251735171344</v>
+        <v>1.259766727281851</v>
       </c>
     </row>
     <row r="266">
@@ -4153,13 +4153,13 @@
         <v>0.09</v>
       </c>
       <c r="B266" t="n">
-        <v>0.05583093276632445</v>
+        <v>0.06904633692493367</v>
       </c>
       <c r="C266" t="n">
-        <v>0.03416906723367555</v>
+        <v>0.02095366307506633</v>
       </c>
       <c r="D266" t="n">
-        <v>37.9656302596395</v>
+        <v>23.28184786118481</v>
       </c>
     </row>
     <row r="267">
@@ -4167,13 +4167,13 @@
         <v>0.11</v>
       </c>
       <c r="B267" t="n">
-        <v>0.0886391579662078</v>
+        <v>0.08990728062964415</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0213608420337922</v>
+        <v>0.02009271937035585</v>
       </c>
       <c r="D267" t="n">
-        <v>19.41894730344745</v>
+        <v>18.26610851850532</v>
       </c>
     </row>
     <row r="268">
@@ -4181,13 +4181,13 @@
         <v>0.68</v>
       </c>
       <c r="B268" t="n">
-        <v>0.3596766808892506</v>
+        <v>0.3501663424582302</v>
       </c>
       <c r="C268" t="n">
-        <v>0.3203233191107494</v>
+        <v>0.3298336575417699</v>
       </c>
       <c r="D268" t="n">
-        <v>47.10637045746314</v>
+        <v>48.50494963849557</v>
       </c>
     </row>
     <row r="269">
@@ -4195,13 +4195,13 @@
         <v>0.03</v>
       </c>
       <c r="B269" t="n">
-        <v>0.04565482487192807</v>
+        <v>0.04242199054376128</v>
       </c>
       <c r="C269" t="n">
-        <v>0.01565482487192807</v>
+        <v>0.01242199054376128</v>
       </c>
       <c r="D269" t="n">
-        <v>52.18274957309357</v>
+        <v>41.40663514587094</v>
       </c>
     </row>
     <row r="270">
@@ -4209,13 +4209,13 @@
         <v>0.36</v>
       </c>
       <c r="B270" t="n">
-        <v>0.4039781692828134</v>
+        <v>0.4031214730485231</v>
       </c>
       <c r="C270" t="n">
-        <v>0.0439781692828134</v>
+        <v>0.0431214730485231</v>
       </c>
       <c r="D270" t="n">
-        <v>12.21615813411483</v>
+        <v>11.97818695792308</v>
       </c>
     </row>
     <row r="271">
@@ -4223,13 +4223,13 @@
         <v>0.04</v>
       </c>
       <c r="B271" t="n">
-        <v>0.09034723651252696</v>
+        <v>0.08506450746665983</v>
       </c>
       <c r="C271" t="n">
-        <v>0.05034723651252696</v>
+        <v>0.04506450746665983</v>
       </c>
       <c r="D271" t="n">
-        <v>125.8680912813174</v>
+        <v>112.6612686666496</v>
       </c>
     </row>
     <row r="272">
@@ -4237,13 +4237,13 @@
         <v>0.01</v>
       </c>
       <c r="B272" t="n">
-        <v>0.03204882068598358</v>
+        <v>0.03740921129036423</v>
       </c>
       <c r="C272" t="n">
-        <v>0.02204882068598358</v>
+        <v>0.02740921129036423</v>
       </c>
       <c r="D272" t="n">
-        <v>220.4882068598358</v>
+        <v>274.0921129036423</v>
       </c>
     </row>
     <row r="273">
@@ -4251,13 +4251,13 @@
         <v>0.1</v>
       </c>
       <c r="B273" t="n">
-        <v>0.1118587837749606</v>
+        <v>0.08332978723589424</v>
       </c>
       <c r="C273" t="n">
-        <v>0.01185878377496061</v>
+        <v>0.01667021276410577</v>
       </c>
       <c r="D273" t="n">
-        <v>11.85878377496061</v>
+        <v>16.67021276410577</v>
       </c>
     </row>
     <row r="274">
@@ -4265,13 +4265,13 @@
         <v>0.16</v>
       </c>
       <c r="B274" t="n">
-        <v>0.3868360841936526</v>
+        <v>0.3571652521878729</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2268360841936526</v>
+        <v>0.1971652521878729</v>
       </c>
       <c r="D274" t="n">
-        <v>141.7725526210328</v>
+        <v>123.2282826174205</v>
       </c>
     </row>
     <row r="275">
@@ -4279,13 +4279,13 @@
         <v>0.02</v>
       </c>
       <c r="B275" t="n">
-        <v>0.07759988655681394</v>
+        <v>0.01897063667204024</v>
       </c>
       <c r="C275" t="n">
-        <v>0.05759988655681393</v>
+        <v>0.001029363327959758</v>
       </c>
       <c r="D275" t="n">
-        <v>287.9994327840697</v>
+        <v>5.146816639798792</v>
       </c>
     </row>
     <row r="276">
@@ -4293,13 +4293,13 @@
         <v>0.09</v>
       </c>
       <c r="B276" t="n">
-        <v>0.06914869728627848</v>
+        <v>0.06330835315937117</v>
       </c>
       <c r="C276" t="n">
-        <v>0.02085130271372151</v>
+        <v>0.02669164684062883</v>
       </c>
       <c r="D276" t="n">
-        <v>23.16811412635724</v>
+        <v>29.65738537847648</v>
       </c>
     </row>
     <row r="277">
@@ -4307,13 +4307,13 @@
         <v>0.06</v>
       </c>
       <c r="B277" t="n">
-        <v>0.07513777977834579</v>
+        <v>0.09445017510819192</v>
       </c>
       <c r="C277" t="n">
-        <v>0.01513777977834579</v>
+        <v>0.03445017510819193</v>
       </c>
       <c r="D277" t="n">
-        <v>25.22963296390966</v>
+        <v>57.41695851365321</v>
       </c>
     </row>
     <row r="278">
@@ -4321,13 +4321,13 @@
         <v>0.16</v>
       </c>
       <c r="B278" t="n">
-        <v>0.5069882461278882</v>
+        <v>0.5621768110643055</v>
       </c>
       <c r="C278" t="n">
-        <v>0.3469882461278881</v>
+        <v>0.4021768110643055</v>
       </c>
       <c r="D278" t="n">
-        <v>216.8676538299301</v>
+        <v>251.3605069151909</v>
       </c>
     </row>
     <row r="279">
@@ -4335,13 +4335,13 @@
         <v>0.13</v>
       </c>
       <c r="B279" t="n">
-        <v>0.1052503011179898</v>
+        <v>0.1211929166438873</v>
       </c>
       <c r="C279" t="n">
-        <v>0.02474969888201017</v>
+        <v>0.008807083356112688</v>
       </c>
       <c r="D279" t="n">
-        <v>19.03822990923859</v>
+        <v>6.774679504702068</v>
       </c>
     </row>
     <row r="280">
@@ -4349,13 +4349,13 @@
         <v>0.11</v>
       </c>
       <c r="B280" t="n">
-        <v>0.06256242820386837</v>
+        <v>0.0951047210274566</v>
       </c>
       <c r="C280" t="n">
-        <v>0.04743757179613163</v>
+        <v>0.0148952789725434</v>
       </c>
       <c r="D280" t="n">
-        <v>43.12506526921057</v>
+        <v>13.54116270231219</v>
       </c>
     </row>
     <row r="281">
@@ -4363,13 +4363,13 @@
         <v>0.02</v>
       </c>
       <c r="B281" t="n">
-        <v>0.0607155120143249</v>
+        <v>0.003739633053260027</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0407155120143249</v>
+        <v>0.01626036694673997</v>
       </c>
       <c r="D281" t="n">
-        <v>203.5775600716245</v>
+        <v>81.30183473369986</v>
       </c>
     </row>
     <row r="282">
@@ -4377,13 +4377,13 @@
         <v>0.4</v>
       </c>
       <c r="B282" t="n">
-        <v>0.3812817609592388</v>
+        <v>0.365985775491086</v>
       </c>
       <c r="C282" t="n">
-        <v>0.0187182390407612</v>
+        <v>0.03401422450891406</v>
       </c>
       <c r="D282" t="n">
-        <v>4.679559760190299</v>
+        <v>8.503556127228515</v>
       </c>
     </row>
     <row r="283">
@@ -4391,13 +4391,13 @@
         <v>0.29</v>
       </c>
       <c r="B283" t="n">
-        <v>0.1722389206300802</v>
+        <v>0.1749042342745706</v>
       </c>
       <c r="C283" t="n">
-        <v>0.1177610793699198</v>
+        <v>0.1150957657254294</v>
       </c>
       <c r="D283" t="n">
-        <v>40.6072687482482</v>
+        <v>39.68819507773428</v>
       </c>
     </row>
     <row r="284">
@@ -4405,13 +4405,13 @@
         <v>0.05</v>
       </c>
       <c r="B284" t="n">
-        <v>0.1066952410884286</v>
+        <v>0.1373577484258169</v>
       </c>
       <c r="C284" t="n">
-        <v>0.05669524108842865</v>
+        <v>0.08735774842581694</v>
       </c>
       <c r="D284" t="n">
-        <v>113.3904821768573</v>
+        <v>174.7154968516338</v>
       </c>
     </row>
     <row r="285">
@@ -4419,13 +4419,13 @@
         <v>0.03</v>
       </c>
       <c r="B285" t="n">
-        <v>0.1559997331550195</v>
+        <v>0.1597953330858975</v>
       </c>
       <c r="C285" t="n">
-        <v>0.1259997331550195</v>
+        <v>0.1297953330858975</v>
       </c>
       <c r="D285" t="n">
-        <v>419.9991105167315</v>
+        <v>432.651110286325</v>
       </c>
     </row>
     <row r="286">
@@ -4433,13 +4433,13 @@
         <v>0.54</v>
       </c>
       <c r="B286" t="n">
-        <v>0.4948364213079924</v>
+        <v>0.4495670648894137</v>
       </c>
       <c r="C286" t="n">
-        <v>0.0451635786920076</v>
+        <v>0.09043293511058637</v>
       </c>
       <c r="D286" t="n">
-        <v>8.363625683705109</v>
+        <v>16.74683983529377</v>
       </c>
     </row>
     <row r="287">
@@ -4447,13 +4447,13 @@
         <v>0.02</v>
       </c>
       <c r="B287" t="n">
-        <v>0.02400505444325018</v>
+        <v>0.03336642201069534</v>
       </c>
       <c r="C287" t="n">
-        <v>0.004005054443250184</v>
+        <v>0.01336642201069534</v>
       </c>
       <c r="D287" t="n">
-        <v>20.02527221625092</v>
+        <v>66.8321100534767</v>
       </c>
     </row>
     <row r="288">
@@ -4461,13 +4461,13 @@
         <v>0.17</v>
       </c>
       <c r="B288" t="n">
-        <v>0.08199522670260351</v>
+        <v>0.08280586597566775</v>
       </c>
       <c r="C288" t="n">
-        <v>0.0880047732973965</v>
+        <v>0.08719413402433226</v>
       </c>
       <c r="D288" t="n">
-        <v>51.76751370435088</v>
+        <v>51.29066707313662</v>
       </c>
     </row>
     <row r="289">
@@ -4475,13 +4475,13 @@
         <v>0.05</v>
       </c>
       <c r="B289" t="n">
-        <v>0.05714173523985566</v>
+        <v>0.05271488113691358</v>
       </c>
       <c r="C289" t="n">
-        <v>0.007141735239855659</v>
+        <v>0.00271488113691358</v>
       </c>
       <c r="D289" t="n">
-        <v>14.28347047971132</v>
+        <v>5.42976227382716</v>
       </c>
     </row>
     <row r="290">
@@ -4489,10 +4489,10 @@
         <v>0</v>
       </c>
       <c r="B290" t="n">
-        <v>0.06677715151003838</v>
+        <v>0.06313698103107801</v>
       </c>
       <c r="C290" t="n">
-        <v>0.06677715151003838</v>
+        <v>0.06313698103107801</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -4505,13 +4505,13 @@
         <v>0.38</v>
       </c>
       <c r="B291" t="n">
-        <v>0.3348657217548172</v>
+        <v>0.2903971989482551</v>
       </c>
       <c r="C291" t="n">
-        <v>0.04513427824518285</v>
+        <v>0.0896028010517449</v>
       </c>
       <c r="D291" t="n">
-        <v>11.87744164346917</v>
+        <v>23.57968448730129</v>
       </c>
     </row>
     <row r="292">
@@ -4519,13 +4519,13 @@
         <v>0.08</v>
       </c>
       <c r="B292" t="n">
-        <v>0.07680708294477723</v>
+        <v>0.06618223161566666</v>
       </c>
       <c r="C292" t="n">
-        <v>0.003192917055222774</v>
+        <v>0.01381776838433334</v>
       </c>
       <c r="D292" t="n">
-        <v>3.991146319028468</v>
+        <v>17.27221048041667</v>
       </c>
     </row>
     <row r="293">
@@ -4533,13 +4533,13 @@
         <v>0.12</v>
       </c>
       <c r="B293" t="n">
-        <v>0.1266894590552084</v>
+        <v>0.11248850142394</v>
       </c>
       <c r="C293" t="n">
-        <v>0.006689459055208402</v>
+        <v>0.007511498576060038</v>
       </c>
       <c r="D293" t="n">
-        <v>5.574549212673668</v>
+        <v>6.259582146716699</v>
       </c>
     </row>
     <row r="294">
@@ -4547,13 +4547,13 @@
         <v>0.37</v>
       </c>
       <c r="B294" t="n">
-        <v>0.2147053379354922</v>
+        <v>0.2268131599207659</v>
       </c>
       <c r="C294" t="n">
-        <v>0.1552946620645078</v>
+        <v>0.143186840079234</v>
       </c>
       <c r="D294" t="n">
-        <v>41.97153028770482</v>
+        <v>38.69914596736056</v>
       </c>
     </row>
     <row r="295">
@@ -4561,13 +4561,13 @@
         <v>0.16</v>
       </c>
       <c r="B295" t="n">
-        <v>0.108190076025489</v>
+        <v>0.1000801372892674</v>
       </c>
       <c r="C295" t="n">
-        <v>0.05180992397451098</v>
+        <v>0.0599198627107326</v>
       </c>
       <c r="D295" t="n">
-        <v>32.38120248406936</v>
+        <v>37.44991419420787</v>
       </c>
     </row>
     <row r="296">
@@ -4575,13 +4575,13 @@
         <v>0.13</v>
       </c>
       <c r="B296" t="n">
-        <v>0.1019067378772588</v>
+        <v>0.1108902455842847</v>
       </c>
       <c r="C296" t="n">
-        <v>0.02809326212274121</v>
+        <v>0.01910975441571533</v>
       </c>
       <c r="D296" t="n">
-        <v>21.61020163287786</v>
+        <v>14.69981108901179</v>
       </c>
     </row>
     <row r="297">
@@ -4589,13 +4589,13 @@
         <v>0.43</v>
       </c>
       <c r="B297" t="n">
-        <v>0.321869109307666</v>
+        <v>0.3476814184311405</v>
       </c>
       <c r="C297" t="n">
-        <v>0.1081308906923339</v>
+        <v>0.08231858156885946</v>
       </c>
       <c r="D297" t="n">
-        <v>25.14671876565906</v>
+        <v>19.14385617880453</v>
       </c>
     </row>
     <row r="298">
@@ -4603,13 +4603,13 @@
         <v>0.05</v>
       </c>
       <c r="B298" t="n">
-        <v>0.3170496830961673</v>
+        <v>0.3173826438747478</v>
       </c>
       <c r="C298" t="n">
-        <v>0.2670496830961673</v>
+        <v>0.2673826438747478</v>
       </c>
       <c r="D298" t="n">
-        <v>534.0993661923346</v>
+        <v>534.7652877494955</v>
       </c>
     </row>
     <row r="299">
@@ -4617,13 +4617,13 @@
         <v>0.36</v>
       </c>
       <c r="B299" t="n">
-        <v>0.6681796571414176</v>
+        <v>0.583591142357053</v>
       </c>
       <c r="C299" t="n">
-        <v>0.3081796571414176</v>
+        <v>0.223591142357053</v>
       </c>
       <c r="D299" t="n">
-        <v>85.60546031706045</v>
+        <v>62.10865065473696</v>
       </c>
     </row>
     <row r="300">
@@ -4631,13 +4631,13 @@
         <v>0.12</v>
       </c>
       <c r="B300" t="n">
-        <v>0.3143838436164033</v>
+        <v>0.2954161250715054</v>
       </c>
       <c r="C300" t="n">
-        <v>0.1943838436164033</v>
+        <v>0.1754161250715054</v>
       </c>
       <c r="D300" t="n">
-        <v>161.9865363470027</v>
+        <v>146.1801042262545</v>
       </c>
     </row>
     <row r="301">
@@ -4645,13 +4645,13 @@
         <v>0.67</v>
       </c>
       <c r="B301" t="n">
-        <v>0.611549778254223</v>
+        <v>0.5158676020432512</v>
       </c>
       <c r="C301" t="n">
-        <v>0.05845022174577708</v>
+        <v>0.1541323979567488</v>
       </c>
       <c r="D301" t="n">
-        <v>8.723913693399563</v>
+        <v>23.00483551593266</v>
       </c>
     </row>
   </sheetData>
